--- a/batch_results.xlsx
+++ b/batch_results.xlsx
@@ -129,17 +129,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFD966"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -169,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -199,24 +199,15 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -228,10 +219,10 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -804,7 +795,7 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>19.7</v>
+        <v>17.7</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -902,7 +893,7 @@
         </is>
       </c>
       <c r="E5" s="10" t="n">
-        <v>20.2</v>
+        <v>15.9</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -939,9 +930,9 @@
           <t>19</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr">
-        <is>
-          <t>29</t>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>19</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
@@ -974,9 +965,9 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T5" s="12" t="inlineStr">
-        <is>
-          <t>6/7</t>
+      <c r="T5" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
         </is>
       </c>
     </row>
@@ -1000,7 +991,7 @@
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>12.8</v>
+        <v>10.5</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -1098,7 +1089,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -1196,7 +1187,7 @@
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>13.6</v>
+        <v>11.2</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
@@ -1294,7 +1285,7 @@
         </is>
       </c>
       <c r="E9" s="10" t="n">
-        <v>39.5</v>
+        <v>30.7</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
@@ -1392,7 +1383,7 @@
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>46</v>
+        <v>33.5</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
@@ -1490,7 +1481,7 @@
         </is>
       </c>
       <c r="E11" s="10" t="n">
-        <v>77.8</v>
+        <v>32.2</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
@@ -1588,7 +1579,7 @@
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>71.2</v>
+        <v>34.7</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1677,7 @@
         </is>
       </c>
       <c r="E13" s="10" t="n">
-        <v>28.5</v>
+        <v>19.7</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -1765,159 +1756,159 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>ACCURACY SUMMARY</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Accuracy %</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n"/>
-      <c r="C16" s="15" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G16" s="15" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I16" s="15" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="K16" s="17" t="inlineStr">
+      <c r="K16" s="15" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="L16" s="16" t="inlineStr">
-        <is>
-          <t>9/10</t>
-        </is>
-      </c>
-      <c r="M16" s="18" t="inlineStr">
-        <is>
-          <t>90.0%</t>
-        </is>
-      </c>
-      <c r="N16" s="16" t="inlineStr">
+      <c r="L16" s="14" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="O16" s="17" t="inlineStr">
+      <c r="M16" s="15" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="P16" s="16" t="inlineStr">
+      <c r="N16" s="14" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="Q16" s="17" t="inlineStr">
+      <c r="O16" s="15" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="R16" s="16" t="inlineStr">
+      <c r="P16" s="14" t="inlineStr">
         <is>
           <t>10/10</t>
         </is>
       </c>
-      <c r="S16" s="17" t="inlineStr">
+      <c r="Q16" s="15" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="R16" s="14" t="inlineStr">
+        <is>
+          <t>10/10</t>
+        </is>
+      </c>
+      <c r="S16" s="15" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>All Correct</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
-        <is>
-          <t>9 / 10  (90.0%)</t>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>10 / 10  (100.0%)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>Legend:</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>Correct prediction</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>Wrong prediction</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>Ground truth value</t>
         </is>
       </c>
-      <c r="G20" s="26" t="inlineStr">
+      <c r="G20" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
-      <c r="H20" s="23" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>All vitals correct</t>
         </is>
       </c>
-      <c r="I20" s="27" t="inlineStr">
+      <c r="I20" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
-      <c r="J20" s="23" t="inlineStr">
+      <c r="J20" s="20" t="inlineStr">
         <is>
           <t>Some vitals wrong</t>
         </is>

--- a/batch_results.xlsx
+++ b/batch_results.xlsx
@@ -80,7 +80,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -129,17 +129,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFD966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -169,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -199,30 +204,39 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -588,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:T109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -795,7 +809,7 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>17.7</v>
+        <v>28</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -893,7 +907,7 @@
         </is>
       </c>
       <c r="E5" s="10" t="n">
-        <v>15.9</v>
+        <v>27.4</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -991,7 +1005,7 @@
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>10.5</v>
+        <v>19.6</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -1089,7 +1103,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>10.5</v>
+        <v>17.8</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -1173,30 +1187,30 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>02_01_1</t>
+          <t>01_03_1</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>11.2</v>
+        <v>45.9</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1211,42 +1225,42 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>73</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>73</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>109/70</t>
+          <t>97/55</t>
         </is>
       </c>
       <c r="O8" s="8" t="inlineStr">
         <is>
-          <t>109/70</t>
+          <t>97/55</t>
         </is>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>81</t>
         </is>
       </c>
       <c r="Q8" s="8" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>81</t>
         </is>
       </c>
       <c r="R8" s="7" t="inlineStr">
@@ -1254,14 +1268,10 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="T8" s="9" t="inlineStr">
-        <is>
-          <t>7/7</t>
+      <c r="S8" s="11" t="inlineStr"/>
+      <c r="T8" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
         </is>
       </c>
     </row>
@@ -1271,80 +1281,80 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>03_01_1</t>
+          <t>01_03_2</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="E9" s="10" t="n">
-        <v>30.7</v>
+        <v>37.4</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>73</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>73</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M9" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>100/38</t>
+          <t>97/55</t>
         </is>
       </c>
       <c r="O9" s="8" t="inlineStr">
         <is>
-          <t>100/38</t>
+          <t>97/55</t>
         </is>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>81</t>
         </is>
       </c>
       <c r="Q9" s="8" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>81</t>
         </is>
       </c>
       <c r="R9" s="7" t="inlineStr">
@@ -1352,14 +1362,10 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="S9" s="8" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="T9" s="9" t="inlineStr">
-        <is>
-          <t>7/7</t>
+      <c r="S9" s="11" t="inlineStr"/>
+      <c r="T9" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
         </is>
       </c>
     </row>
@@ -1369,80 +1375,80 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>03_01_2</t>
+          <t>01_04_1</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>33.5</v>
+        <v>29.1</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K10" s="8" t="inlineStr">
-        <is>
-          <t>93</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>73</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M10" s="8" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>14</t>
         </is>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>100/38</t>
+          <t>97/55</t>
         </is>
       </c>
       <c r="O10" s="8" t="inlineStr">
         <is>
-          <t>100/38</t>
+          <t>97/55</t>
         </is>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>81</t>
         </is>
       </c>
       <c r="Q10" s="8" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>81</t>
         </is>
       </c>
       <c r="R10" s="7" t="inlineStr">
@@ -1455,9 +1461,9 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T10" s="9" t="inlineStr">
-        <is>
-          <t>7/7</t>
+      <c r="T10" s="12" t="inlineStr">
+        <is>
+          <t>5/7</t>
         </is>
       </c>
     </row>
@@ -1467,50 +1473,50 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>03_02_1</t>
+          <t>01_04_2</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="E11" s="10" t="n">
-        <v>32.2</v>
+        <v>38</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>73</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>73</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -1518,44 +1524,40 @@
           <t>14</t>
         </is>
       </c>
-      <c r="M11" s="8" t="inlineStr">
-        <is>
-          <t>14</t>
+      <c r="M11" s="11" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>108/75</t>
+          <t>97/55</t>
         </is>
       </c>
       <c r="O11" s="8" t="inlineStr">
         <is>
-          <t>108/75</t>
+          <t>97/55</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>81</t>
         </is>
       </c>
       <c r="Q11" s="8" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>81</t>
         </is>
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="S11" s="8" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="T11" s="9" t="inlineStr">
-        <is>
-          <t>7/7</t>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S11" s="11" t="inlineStr"/>
+      <c r="T11" s="12" t="inlineStr">
+        <is>
+          <t>5/7</t>
         </is>
       </c>
     </row>
@@ -1565,90 +1567,90 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>03_02_2</t>
+          <t>01_05_1</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>34.7</v>
+        <v>28.9</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>73</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>76</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>108/75</t>
+          <t>94/78</t>
         </is>
       </c>
       <c r="O12" s="8" t="inlineStr">
         <is>
-          <t>108/75</t>
+          <t>94/78</t>
         </is>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>83</t>
         </is>
       </c>
       <c r="Q12" s="8" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>83</t>
         </is>
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="S12" s="8" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="T12" s="9" t="inlineStr">
@@ -1663,252 +1665,8910 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
+          <t>01_05_2</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>94/78</t>
+        </is>
+      </c>
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>94/78</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R13" s="7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S13" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T13" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>01_06_1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="K14" s="11" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>97/55</t>
+        </is>
+      </c>
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>97/55</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="R14" s="7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S14" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T14" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>01_06_2</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>97/55</t>
+        </is>
+      </c>
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>97/55</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="R15" s="7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S15" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T15" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>01_07_1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>138/83</t>
+        </is>
+      </c>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>138/83</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="R16" s="7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S16" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T16" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>01_07_2</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>138/83</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>138/83</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="R17" s="7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S17" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T17" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>01_08_1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>94/78</t>
+        </is>
+      </c>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>94/78</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R18" s="7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S18" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T18" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>01_08_2</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>94/78</t>
+        </is>
+      </c>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>94/78</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="Q19" s="8" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R19" s="7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S19" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T19" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>01_09_1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>97/55</t>
+        </is>
+      </c>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>97/55</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="Q20" s="8" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="R20" s="7" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="S20" s="8" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="T20" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>01_09_2</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M21" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>97/55</t>
+        </is>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>97/55</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="R21" s="7" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="S21" s="8" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="T21" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>01_10_1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>97/55</t>
+        </is>
+      </c>
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>97/55</t>
+        </is>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="R22" s="7" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="S22" s="8" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="T22" s="12" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>01_10_2</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K23" s="11" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M23" s="8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>97/55</t>
+        </is>
+      </c>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>97/55</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="Q23" s="8" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="R23" s="7" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="S23" s="8" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="T23" s="12" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>02_01_1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <t>109/70</t>
+        </is>
+      </c>
+      <c r="O24" s="8" t="inlineStr">
+        <is>
+          <t>109/70</t>
+        </is>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R24" s="7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S24" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T24" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>02_01_2</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>109/70</t>
+        </is>
+      </c>
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>109/70</t>
+        </is>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R25" s="7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S25" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T25" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>02_02_1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>109/70</t>
+        </is>
+      </c>
+      <c r="O26" s="8" t="inlineStr">
+        <is>
+          <t>109/70</t>
+        </is>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="Q26" s="8" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R26" s="7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S26" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T26" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>02_02_2</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>109/70</t>
+        </is>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>109/70</t>
+        </is>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="Q27" s="8" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R27" s="7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S27" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T27" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>02_03_1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>108/75</t>
+        </is>
+      </c>
+      <c r="O28" s="8" t="inlineStr">
+        <is>
+          <t>108/75</t>
+        </is>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="R28" s="7" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="S28" s="8" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="T28" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>02_03_2</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M29" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>108/75</t>
+        </is>
+      </c>
+      <c r="O29" s="8" t="inlineStr">
+        <is>
+          <t>108/75</t>
+        </is>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="Q29" s="8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="R29" s="7" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="S29" s="8" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="T29" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>02_04_1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K30" s="11" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>108/75</t>
+        </is>
+      </c>
+      <c r="O30" s="8" t="inlineStr">
+        <is>
+          <t>108/75</t>
+        </is>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="Q30" s="11" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="R30" s="7" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="S30" s="8" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="T30" s="12" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>02_04_2</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>108/75</t>
+        </is>
+      </c>
+      <c r="O31" s="8" t="inlineStr">
+        <is>
+          <t>108/75</t>
+        </is>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="Q31" s="11" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="R31" s="7" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="S31" s="8" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="T31" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>02_05_1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M32" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="inlineStr">
+        <is>
+          <t>119/76</t>
+        </is>
+      </c>
+      <c r="O32" s="8" t="inlineStr">
+        <is>
+          <t>119/76</t>
+        </is>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="R32" s="7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S32" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T32" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>02_05_2</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M33" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="inlineStr">
+        <is>
+          <t>119/76</t>
+        </is>
+      </c>
+      <c r="O33" s="8" t="inlineStr">
+        <is>
+          <t>119/76</t>
+        </is>
+      </c>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="Q33" s="8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="R33" s="7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S33" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T33" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>02_06_1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N34" s="7" t="inlineStr">
+        <is>
+          <t>119/76</t>
+        </is>
+      </c>
+      <c r="O34" s="8" t="inlineStr">
+        <is>
+          <t>119/76</t>
+        </is>
+      </c>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="Q34" s="8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="R34" s="7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S34" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T34" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>02_06_2</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M35" s="11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="inlineStr">
+        <is>
+          <t>119/76</t>
+        </is>
+      </c>
+      <c r="O35" s="8" t="inlineStr">
+        <is>
+          <t>119/76</t>
+        </is>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="Q35" s="8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="R35" s="7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S35" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T35" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>02_07_1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M36" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="inlineStr">
+        <is>
+          <t>69/57</t>
+        </is>
+      </c>
+      <c r="O36" s="8" t="inlineStr">
+        <is>
+          <t>69/57</t>
+        </is>
+      </c>
+      <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="Q36" s="8" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R36" s="7" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="S36" s="8" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="T36" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>02_07_2</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M37" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>69/57</t>
+        </is>
+      </c>
+      <c r="O37" s="8" t="inlineStr">
+        <is>
+          <t>69/57</t>
+        </is>
+      </c>
+      <c r="P37" s="7" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="Q37" s="8" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R37" s="7" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="S37" s="8" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="T37" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>02_08_1</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="inlineStr">
+        <is>
+          <t>69/57</t>
+        </is>
+      </c>
+      <c r="O38" s="8" t="inlineStr">
+        <is>
+          <t>69/57</t>
+        </is>
+      </c>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="Q38" s="8" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R38" s="7" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="S38" s="8" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="T38" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>02_08_2</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="K39" s="8" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M39" s="11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>69/57</t>
+        </is>
+      </c>
+      <c r="O39" s="8" t="inlineStr">
+        <is>
+          <t>69/57</t>
+        </is>
+      </c>
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="Q39" s="8" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R39" s="7" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="S39" s="8" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="T39" s="12" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>02_09_1</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K40" s="11" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M40" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="inlineStr">
+        <is>
+          <t>109/75</t>
+        </is>
+      </c>
+      <c r="O40" s="8" t="inlineStr">
+        <is>
+          <t>109/75</t>
+        </is>
+      </c>
+      <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="Q40" s="8" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="R40" s="7" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="S40" s="8" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="T40" s="12" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>02_09_2</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M41" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="inlineStr">
+        <is>
+          <t>109/75</t>
+        </is>
+      </c>
+      <c r="O41" s="8" t="inlineStr">
+        <is>
+          <t>109/75</t>
+        </is>
+      </c>
+      <c r="P41" s="7" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="Q41" s="8" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="R41" s="7" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="S41" s="8" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="T41" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>02_10_1</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M42" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N42" s="7" t="inlineStr">
+        <is>
+          <t>109/70</t>
+        </is>
+      </c>
+      <c r="O42" s="8" t="inlineStr">
+        <is>
+          <t>109/70</t>
+        </is>
+      </c>
+      <c r="P42" s="7" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="Q42" s="8" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R42" s="7" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="S42" s="8" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="T42" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>02_10_2</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K43" s="11" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M43" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>109/70</t>
+        </is>
+      </c>
+      <c r="O43" s="8" t="inlineStr">
+        <is>
+          <t>109/70</t>
+        </is>
+      </c>
+      <c r="P43" s="7" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="Q43" s="8" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R43" s="7" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="S43" s="8" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="T43" s="12" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>03_01_1</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M44" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="inlineStr">
+        <is>
+          <t>100/38</t>
+        </is>
+      </c>
+      <c r="O44" s="8" t="inlineStr">
+        <is>
+          <t>100/38</t>
+        </is>
+      </c>
+      <c r="P44" s="7" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="Q44" s="8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="R44" s="7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S44" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T44" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>03_01_2</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="K45" s="8" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M45" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>100/38</t>
+        </is>
+      </c>
+      <c r="O45" s="8" t="inlineStr">
+        <is>
+          <t>100/38</t>
+        </is>
+      </c>
+      <c r="P45" s="7" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="Q45" s="8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="R45" s="7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S45" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T45" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>03_02_1</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K46" s="11" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N46" s="7" t="inlineStr">
+        <is>
+          <t>108/75</t>
+        </is>
+      </c>
+      <c r="O46" s="8" t="inlineStr">
+        <is>
+          <t>108/75</t>
+        </is>
+      </c>
+      <c r="P46" s="7" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="Q46" s="8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="R46" s="7" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="S46" s="8" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="T46" s="12" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>03_02_2</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K47" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M47" s="8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>108/75</t>
+        </is>
+      </c>
+      <c r="O47" s="8" t="inlineStr">
+        <is>
+          <t>108/75</t>
+        </is>
+      </c>
+      <c r="P47" s="7" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="Q47" s="8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="R47" s="7" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="S47" s="8" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="T47" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>03_03_1</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M48" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="inlineStr">
+        <is>
+          <t>118/67</t>
+        </is>
+      </c>
+      <c r="O48" s="8" t="inlineStr">
+        <is>
+          <t>118/67</t>
+        </is>
+      </c>
+      <c r="P48" s="7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="Q48" s="8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="R48" s="7" t="inlineStr">
+        <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="S48" s="8" t="inlineStr">
+        <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="T48" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>03_03_2</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K49" s="8" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M49" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="inlineStr">
+        <is>
+          <t>118/67</t>
+        </is>
+      </c>
+      <c r="O49" s="8" t="inlineStr">
+        <is>
+          <t>118/67</t>
+        </is>
+      </c>
+      <c r="P49" s="7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="Q49" s="8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="R49" s="7" t="inlineStr">
+        <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="S49" s="8" t="inlineStr">
+        <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="T49" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>03_04_1</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M50" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N50" s="7" t="inlineStr">
+        <is>
+          <t>117/81</t>
+        </is>
+      </c>
+      <c r="O50" s="8" t="inlineStr">
+        <is>
+          <t>117/81</t>
+        </is>
+      </c>
+      <c r="P50" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="Q50" s="8" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="R50" s="7" t="inlineStr">
+        <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="S50" s="8" t="inlineStr">
+        <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="T50" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>03_04_2</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K51" s="8" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M51" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="inlineStr">
+        <is>
+          <t>117/81</t>
+        </is>
+      </c>
+      <c r="O51" s="8" t="inlineStr">
+        <is>
+          <t>117/81</t>
+        </is>
+      </c>
+      <c r="P51" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="Q51" s="8" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="R51" s="7" t="inlineStr">
+        <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="S51" s="8" t="inlineStr">
+        <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="T51" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>03_05_1</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K52" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M52" s="11" t="inlineStr"/>
+      <c r="N52" s="7" t="inlineStr">
+        <is>
+          <t>118/67</t>
+        </is>
+      </c>
+      <c r="O52" s="8" t="inlineStr">
+        <is>
+          <t>118/67</t>
+        </is>
+      </c>
+      <c r="P52" s="7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="Q52" s="8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="R52" s="7" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="S52" s="8" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="T52" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>03_05_2</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="K53" s="8" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M53" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N53" s="7" t="inlineStr">
+        <is>
+          <t>118/67</t>
+        </is>
+      </c>
+      <c r="O53" s="8" t="inlineStr">
+        <is>
+          <t>118/67</t>
+        </is>
+      </c>
+      <c r="P53" s="7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="Q53" s="8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="R53" s="7" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="S53" s="8" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="T53" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>03_06_1</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K54" s="8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M54" s="11" t="inlineStr"/>
+      <c r="N54" s="7" t="inlineStr">
+        <is>
+          <t>118/67</t>
+        </is>
+      </c>
+      <c r="O54" s="8" t="inlineStr">
+        <is>
+          <t>118/67</t>
+        </is>
+      </c>
+      <c r="P54" s="7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="Q54" s="8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="R54" s="7" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="S54" s="8" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="T54" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>03_06_2</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K55" s="8" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M55" s="11" t="inlineStr"/>
+      <c r="N55" s="7" t="inlineStr">
+        <is>
+          <t>118/67</t>
+        </is>
+      </c>
+      <c r="O55" s="8" t="inlineStr">
+        <is>
+          <t>118/67</t>
+        </is>
+      </c>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="Q55" s="8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="R55" s="7" t="inlineStr">
+        <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="S55" s="8" t="inlineStr">
+        <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="T55" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>03_07_1</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="K56" s="11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M56" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N56" s="7" t="inlineStr">
+        <is>
+          <t>117/81</t>
+        </is>
+      </c>
+      <c r="O56" s="8" t="inlineStr">
+        <is>
+          <t>117/81</t>
+        </is>
+      </c>
+      <c r="P56" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="Q56" s="8" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="R56" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S56" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T56" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>03_07_2</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="K57" s="8" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M57" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N57" s="7" t="inlineStr">
+        <is>
+          <t>117/81</t>
+        </is>
+      </c>
+      <c r="O57" s="8" t="inlineStr">
+        <is>
+          <t>117/81</t>
+        </is>
+      </c>
+      <c r="P57" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="Q57" s="8" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="R57" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S57" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T57" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>03_08_1</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="J58" s="7" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="K58" s="8" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M58" s="8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N58" s="7" t="inlineStr">
+        <is>
+          <t>100/61</t>
+        </is>
+      </c>
+      <c r="O58" s="8" t="inlineStr">
+        <is>
+          <t>100/61</t>
+        </is>
+      </c>
+      <c r="P58" s="7" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="Q58" s="8" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="R58" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S58" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T58" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>03_08_2</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="K59" s="8" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M59" s="8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N59" s="7" t="inlineStr">
+        <is>
+          <t>100/61</t>
+        </is>
+      </c>
+      <c r="O59" s="8" t="inlineStr">
+        <is>
+          <t>100/61</t>
+        </is>
+      </c>
+      <c r="P59" s="7" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="Q59" s="8" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="R59" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S59" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T59" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>03_09_1</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="J60" s="7" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K60" s="8" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M60" s="8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N60" s="7" t="inlineStr">
+        <is>
+          <t>117/81</t>
+        </is>
+      </c>
+      <c r="O60" s="8" t="inlineStr">
+        <is>
+          <t>117/81</t>
+        </is>
+      </c>
+      <c r="P60" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="Q60" s="8" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="R60" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S60" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T60" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>03_09_2</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="G61" s="11" t="inlineStr"/>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I61" s="11" t="inlineStr"/>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K61" s="11" t="inlineStr"/>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M61" s="11" t="inlineStr"/>
+      <c r="N61" s="7" t="inlineStr">
+        <is>
+          <t>117/81</t>
+        </is>
+      </c>
+      <c r="O61" s="11" t="inlineStr"/>
+      <c r="P61" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="Q61" s="11" t="inlineStr"/>
+      <c r="R61" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S61" s="11" t="inlineStr"/>
+      <c r="T61" s="13" t="inlineStr">
+        <is>
+          <t>0/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>03_10_1</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="K62" s="8" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M62" s="8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N62" s="7" t="inlineStr">
+        <is>
+          <t>117/81</t>
+        </is>
+      </c>
+      <c r="O62" s="8" t="inlineStr">
+        <is>
+          <t>117/81</t>
+        </is>
+      </c>
+      <c r="P62" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="Q62" s="8" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="R62" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S62" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T62" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>03_10_2</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K63" s="11" t="inlineStr"/>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M63" s="8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N63" s="7" t="inlineStr">
+        <is>
+          <t>117/81</t>
+        </is>
+      </c>
+      <c r="O63" s="8" t="inlineStr">
+        <is>
+          <t>117/81</t>
+        </is>
+      </c>
+      <c r="P63" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="Q63" s="8" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="R63" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S63" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T63" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
           <t>04_01_1</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="E13" s="10" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="E64" s="6" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G64" s="8" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H64" s="7" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I64" s="8" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J64" s="7" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="K64" s="8" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="L64" s="7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M64" s="8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N13" s="7" t="inlineStr">
+      <c r="N64" s="7" t="inlineStr">
         <is>
           <t>115/74</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
+      <c r="O64" s="8" t="inlineStr">
         <is>
           <t>115/74</t>
         </is>
       </c>
-      <c r="P13" s="7" t="inlineStr">
+      <c r="P64" s="7" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="Q13" s="8" t="inlineStr">
+      <c r="Q64" s="8" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="R13" s="7" t="inlineStr">
+      <c r="R64" s="7" t="inlineStr">
         <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="S13" s="8" t="inlineStr">
+      <c r="S64" s="8" t="inlineStr">
         <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="T13" s="9" t="inlineStr">
+      <c r="T64" s="9" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>04_01_2</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="K65" s="8" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M65" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N65" s="7" t="inlineStr">
+        <is>
+          <t>115/74</t>
+        </is>
+      </c>
+      <c r="O65" s="8" t="inlineStr">
+        <is>
+          <t>115/74</t>
+        </is>
+      </c>
+      <c r="P65" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="Q65" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R65" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S65" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T65" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>04_02_1</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="K66" s="8" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M66" s="8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N66" s="7" t="inlineStr">
+        <is>
+          <t>115/74</t>
+        </is>
+      </c>
+      <c r="O66" s="8" t="inlineStr">
+        <is>
+          <t>115/74</t>
+        </is>
+      </c>
+      <c r="P66" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="Q66" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R66" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S66" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T66" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>04_02_2</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K67" s="8" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M67" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N67" s="7" t="inlineStr">
+        <is>
+          <t>115/74</t>
+        </is>
+      </c>
+      <c r="O67" s="8" t="inlineStr">
+        <is>
+          <t>115/74</t>
+        </is>
+      </c>
+      <c r="P67" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="Q67" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R67" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S67" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T67" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>04_03_1</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="J68" s="7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K68" s="8" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M68" s="11" t="inlineStr"/>
+      <c r="N68" s="7" t="inlineStr">
+        <is>
+          <t>123/80</t>
+        </is>
+      </c>
+      <c r="O68" s="8" t="inlineStr">
+        <is>
+          <t>123/80</t>
+        </is>
+      </c>
+      <c r="P68" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="Q68" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R68" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S68" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T68" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>04_03_2</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K69" s="11" t="inlineStr"/>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M69" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N69" s="7" t="inlineStr">
+        <is>
+          <t>123/80</t>
+        </is>
+      </c>
+      <c r="O69" s="8" t="inlineStr">
+        <is>
+          <t>123/80</t>
+        </is>
+      </c>
+      <c r="P69" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="Q69" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R69" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S69" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T69" s="12" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>04_04_1</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G70" s="11" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K70" s="8" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M70" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N70" s="7" t="inlineStr">
+        <is>
+          <t>123/80</t>
+        </is>
+      </c>
+      <c r="O70" s="8" t="inlineStr">
+        <is>
+          <t>123/80</t>
+        </is>
+      </c>
+      <c r="P70" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="Q70" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R70" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S70" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T70" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="n">
+        <v>68</v>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>04_04_2</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K71" s="8" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M71" s="11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N71" s="7" t="inlineStr">
+        <is>
+          <t>123/80</t>
+        </is>
+      </c>
+      <c r="O71" s="8" t="inlineStr">
+        <is>
+          <t>123/80</t>
+        </is>
+      </c>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="Q71" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R71" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S71" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T71" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>04_05_1</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J72" s="7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K72" s="8" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M72" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N72" s="7" t="inlineStr">
+        <is>
+          <t>115/74</t>
+        </is>
+      </c>
+      <c r="O72" s="8" t="inlineStr">
+        <is>
+          <t>115/74</t>
+        </is>
+      </c>
+      <c r="P72" s="7" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="Q72" s="11" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="R72" s="7" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="S72" s="8" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="T72" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>04_05_2</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K73" s="8" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M73" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N73" s="7" t="inlineStr">
+        <is>
+          <t>115/74</t>
+        </is>
+      </c>
+      <c r="O73" s="8" t="inlineStr">
+        <is>
+          <t>115/74</t>
+        </is>
+      </c>
+      <c r="P73" s="7" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="Q73" s="8" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="R73" s="7" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="S73" s="8" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="T73" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>04_06_1</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K74" s="8" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M74" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N74" s="7" t="inlineStr">
+        <is>
+          <t>115/74</t>
+        </is>
+      </c>
+      <c r="O74" s="8" t="inlineStr">
+        <is>
+          <t>115/74</t>
+        </is>
+      </c>
+      <c r="P74" s="7" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="Q74" s="11" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="R74" s="7" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="S74" s="8" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="T74" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>04_06_2</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K75" s="8" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M75" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N75" s="7" t="inlineStr">
+        <is>
+          <t>115/74</t>
+        </is>
+      </c>
+      <c r="O75" s="8" t="inlineStr">
+        <is>
+          <t>115/74</t>
+        </is>
+      </c>
+      <c r="P75" s="7" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="Q75" s="8" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="R75" s="7" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="S75" s="8" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="T75" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>04_07_1</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I76" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J76" s="7" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K76" s="8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="L76" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M76" s="8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N76" s="7" t="inlineStr">
+        <is>
+          <t>97/80</t>
+        </is>
+      </c>
+      <c r="O76" s="8" t="inlineStr">
+        <is>
+          <t>97/80</t>
+        </is>
+      </c>
+      <c r="P76" s="7" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="Q76" s="8" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R76" s="7" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="S76" s="8" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="T76" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>04_07_2</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I77" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K77" s="8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M77" s="8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N77" s="7" t="inlineStr">
+        <is>
+          <t>97/80</t>
+        </is>
+      </c>
+      <c r="O77" s="8" t="inlineStr">
+        <is>
+          <t>97/80</t>
+        </is>
+      </c>
+      <c r="P77" s="7" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="Q77" s="8" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R77" s="7" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="S77" s="8" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="T77" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>04_08_1</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I78" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J78" s="7" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K78" s="11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M78" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N78" s="7" t="inlineStr">
+        <is>
+          <t>97/80</t>
+        </is>
+      </c>
+      <c r="O78" s="8" t="inlineStr">
+        <is>
+          <t>97/80</t>
+        </is>
+      </c>
+      <c r="P78" s="7" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="Q78" s="8" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R78" s="7" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="S78" s="8" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="T78" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>04_08_2</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K79" s="8" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M79" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N79" s="7" t="inlineStr">
+        <is>
+          <t>97/80</t>
+        </is>
+      </c>
+      <c r="O79" s="8" t="inlineStr">
+        <is>
+          <t>97/80</t>
+        </is>
+      </c>
+      <c r="P79" s="7" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="Q79" s="8" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R79" s="7" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="S79" s="8" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="T79" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>04_09_1</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="J80" s="7" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K80" s="11" t="inlineStr"/>
+      <c r="L80" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M80" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N80" s="7" t="inlineStr">
+        <is>
+          <t>119/56</t>
+        </is>
+      </c>
+      <c r="O80" s="8" t="inlineStr">
+        <is>
+          <t>119/56</t>
+        </is>
+      </c>
+      <c r="P80" s="7" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="Q80" s="8" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R80" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S80" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T80" s="12" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>04_09_2</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I81" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J81" s="7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K81" s="11" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M81" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N81" s="7" t="inlineStr">
+        <is>
+          <t>119/56</t>
+        </is>
+      </c>
+      <c r="O81" s="11" t="inlineStr">
+        <is>
+          <t>119/75</t>
+        </is>
+      </c>
+      <c r="P81" s="7" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="Q81" s="8" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R81" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S81" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T81" s="12" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>04_10_1</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J82" s="7" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K82" s="11" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M82" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N82" s="7" t="inlineStr">
+        <is>
+          <t>119/56</t>
+        </is>
+      </c>
+      <c r="O82" s="8" t="inlineStr">
+        <is>
+          <t>119/56</t>
+        </is>
+      </c>
+      <c r="P82" s="7" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="Q82" s="8" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R82" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S82" s="8" t="inlineStr">
+        <is>
+          <t>22.1</t>
+        </is>
+      </c>
+      <c r="T82" s="12" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>05_01_1</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J83" s="7" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="K83" s="8" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M83" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N83" s="7" t="inlineStr">
+        <is>
+          <t>123/80</t>
+        </is>
+      </c>
+      <c r="O83" s="8" t="inlineStr">
+        <is>
+          <t>123/80</t>
+        </is>
+      </c>
+      <c r="P83" s="7" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="Q83" s="8" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="R83" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S83" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T83" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>05_01_2</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="J84" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K84" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L84" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M84" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N84" s="7" t="inlineStr">
+        <is>
+          <t>123/80</t>
+        </is>
+      </c>
+      <c r="O84" s="8" t="inlineStr">
+        <is>
+          <t>123/80</t>
+        </is>
+      </c>
+      <c r="P84" s="7" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="Q84" s="8" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="R84" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S84" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T84" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>05_02_1</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="I85" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J85" s="7" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="K85" s="8" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M85" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N85" s="7" t="inlineStr">
+        <is>
+          <t>123/80</t>
+        </is>
+      </c>
+      <c r="O85" s="8" t="inlineStr">
+        <is>
+          <t>123/80</t>
+        </is>
+      </c>
+      <c r="P85" s="7" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="Q85" s="8" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="R85" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S85" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T85" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>05_02_2</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="J86" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K86" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M86" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N86" s="7" t="inlineStr">
+        <is>
+          <t>123/80</t>
+        </is>
+      </c>
+      <c r="O86" s="8" t="inlineStr">
+        <is>
+          <t>123/80</t>
+        </is>
+      </c>
+      <c r="P86" s="7" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="Q86" s="8" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="R86" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S86" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T86" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>05_03_1</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>130.8</v>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I87" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J87" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="K87" s="8" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M87" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N87" s="7" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="O87" s="8" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="P87" s="7" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="Q87" s="8" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="R87" s="7" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="S87" s="8" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="T87" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>05_03_2</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J88" s="7" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="K88" s="8" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M88" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N88" s="7" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="O88" s="8" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="P88" s="7" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="Q88" s="8" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="R88" s="7" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="S88" s="8" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="T88" s="12" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="n">
+        <v>86</v>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>05_04_1</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I89" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="K89" s="8" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M89" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N89" s="7" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="O89" s="8" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="P89" s="7" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="Q89" s="8" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="R89" s="7" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="S89" s="8" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="T89" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>05_04_2</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="G90" s="8" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I90" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J90" s="7" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="K90" s="8" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="L90" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M90" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N90" s="7" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="O90" s="8" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="P90" s="7" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="Q90" s="8" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="R90" s="7" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="S90" s="8" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="T90" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>05_05_1</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I91" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K91" s="8" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M91" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N91" s="7" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="O91" s="8" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="P91" s="7" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="Q91" s="8" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="R91" s="7" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="S91" s="8" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="T91" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>05_05_2</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J92" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K92" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M92" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N92" s="7" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="O92" s="8" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="P92" s="7" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="Q92" s="8" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="R92" s="7" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="S92" s="8" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="T92" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>05_06_1</t>
+        </is>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I93" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J93" s="7" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K93" s="8" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M93" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N93" s="7" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="O93" s="8" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="P93" s="7" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="Q93" s="8" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="R93" s="7" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="S93" s="8" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="T93" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>05_06_2</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I94" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J94" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K94" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="L94" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M94" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N94" s="7" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="O94" s="8" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="P94" s="7" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="Q94" s="8" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="R94" s="7" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="S94" s="8" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="T94" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>05_07_1</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="I95" s="8" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="K95" s="8" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M95" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N95" s="7" t="inlineStr">
+        <is>
+          <t>69/57</t>
+        </is>
+      </c>
+      <c r="O95" s="8" t="inlineStr">
+        <is>
+          <t>69/57</t>
+        </is>
+      </c>
+      <c r="P95" s="7" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q95" s="8" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="R95" s="7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S95" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T95" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>05_07_2</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G96" s="11" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="J96" s="7" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="K96" s="11" t="inlineStr"/>
+      <c r="L96" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M96" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N96" s="7" t="inlineStr">
+        <is>
+          <t>69/57</t>
+        </is>
+      </c>
+      <c r="O96" s="8" t="inlineStr">
+        <is>
+          <t>69/57</t>
+        </is>
+      </c>
+      <c r="P96" s="7" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="Q96" s="8" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="R96" s="7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S96" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T96" s="12" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>05_08_1</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="I97" s="8" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="K97" s="8" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M97" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N97" s="7" t="inlineStr">
+        <is>
+          <t>69/57</t>
+        </is>
+      </c>
+      <c r="O97" s="8" t="inlineStr">
+        <is>
+          <t>69/57</t>
+        </is>
+      </c>
+      <c r="P97" s="7" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="Q97" s="8" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="R97" s="7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S97" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T97" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>05_08_2</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G98" s="11" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="J98" s="7" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="K98" s="11" t="inlineStr"/>
+      <c r="L98" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M98" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N98" s="7" t="inlineStr">
+        <is>
+          <t>69/57</t>
+        </is>
+      </c>
+      <c r="O98" s="8" t="inlineStr">
+        <is>
+          <t>69/57</t>
+        </is>
+      </c>
+      <c r="P98" s="7" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="Q98" s="8" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="R98" s="7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="S98" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T98" s="12" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="n">
+        <v>96</v>
+      </c>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>05_09_1</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I99" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J99" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K99" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M99" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N99" s="7" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="O99" s="8" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="P99" s="7" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="Q99" s="8" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="R99" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S99" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T99" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>05_09_2</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J100" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="K100" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M100" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N100" s="7" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="O100" s="8" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="P100" s="7" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="Q100" s="8" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="R100" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S100" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T100" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="n">
+        <v>98</v>
+      </c>
+      <c r="B101" s="10" t="inlineStr">
+        <is>
+          <t>05_10_1</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I101" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K101" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M101" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N101" s="7" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="O101" s="8" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="P101" s="7" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="Q101" s="8" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="R101" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S101" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T101" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>05_10_2</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="H102" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I102" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J102" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="K102" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M102" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N102" s="7" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="O102" s="8" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="P102" s="7" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="Q102" s="8" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="R102" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S102" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T102" s="9" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="14" t="inlineStr">
         <is>
           <t>ACCURACY SUMMARY</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="15" t="inlineStr">
         <is>
           <t>Accuracy %</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="14" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="G16" s="15" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="J16" s="14" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="K16" s="15" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="L16" s="14" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="M16" s="15" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N16" s="14" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="O16" s="15" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="P16" s="14" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="Q16" s="15" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="R16" s="14" t="inlineStr">
-        <is>
-          <t>10/10</t>
-        </is>
-      </c>
-      <c r="S16" s="15" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="B105" s="16" t="n"/>
+      <c r="C105" s="16" t="n"/>
+      <c r="D105" s="16" t="n"/>
+      <c r="E105" s="16" t="n"/>
+      <c r="F105" s="17" t="inlineStr">
+        <is>
+          <t>93/99</t>
+        </is>
+      </c>
+      <c r="G105" s="18" t="inlineStr">
+        <is>
+          <t>93.9%</t>
+        </is>
+      </c>
+      <c r="H105" s="17" t="inlineStr">
+        <is>
+          <t>83/99</t>
+        </is>
+      </c>
+      <c r="I105" s="18" t="inlineStr">
+        <is>
+          <t>83.8%</t>
+        </is>
+      </c>
+      <c r="J105" s="17" t="inlineStr">
+        <is>
+          <t>81/99</t>
+        </is>
+      </c>
+      <c r="K105" s="18" t="inlineStr">
+        <is>
+          <t>81.8%</t>
+        </is>
+      </c>
+      <c r="L105" s="17" t="inlineStr">
+        <is>
+          <t>83/99</t>
+        </is>
+      </c>
+      <c r="M105" s="18" t="inlineStr">
+        <is>
+          <t>83.8%</t>
+        </is>
+      </c>
+      <c r="N105" s="17" t="inlineStr">
+        <is>
+          <t>97/99</t>
+        </is>
+      </c>
+      <c r="O105" s="18" t="inlineStr">
+        <is>
+          <t>98.0%</t>
+        </is>
+      </c>
+      <c r="P105" s="17" t="inlineStr">
+        <is>
+          <t>94/99</t>
+        </is>
+      </c>
+      <c r="Q105" s="18" t="inlineStr">
+        <is>
+          <t>94.9%</t>
+        </is>
+      </c>
+      <c r="R105" s="17" t="inlineStr">
+        <is>
+          <t>95/99</t>
+        </is>
+      </c>
+      <c r="S105" s="18" t="inlineStr">
+        <is>
+          <t>96.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="19" t="inlineStr">
         <is>
           <t>All Correct</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>10 / 10  (100.0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="F106" s="20" t="inlineStr">
+        <is>
+          <t>58 / 99  (58.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="21" t="inlineStr">
         <is>
           <t>Legend:</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B109" s="23" t="inlineStr">
         <is>
           <t>Correct prediction</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C109" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D109" s="23" t="inlineStr">
         <is>
           <t>Wrong prediction</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E109" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F109" s="23" t="inlineStr">
         <is>
           <t>Ground truth value</t>
         </is>
       </c>
-      <c r="G20" s="23" t="inlineStr">
+      <c r="G109" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
-      <c r="H20" s="20" t="inlineStr">
+      <c r="H109" s="23" t="inlineStr">
         <is>
           <t>All vitals correct</t>
         </is>
       </c>
-      <c r="I20" s="24" t="inlineStr">
+      <c r="I109" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
-      <c r="J20" s="20" t="inlineStr">
+      <c r="J109" s="23" t="inlineStr">
         <is>
           <t>Some vitals wrong</t>
         </is>
@@ -1917,6 +10577,7 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
+    <mergeCell ref="F106:T106"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="F1:S1"/>
     <mergeCell ref="H2:I2"/>
@@ -1925,8 +10586,7 @@
     <mergeCell ref="R2:S2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="F17:T17"/>
+    <mergeCell ref="A106:E106"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/batch_results.xlsx
+++ b/batch_results.xlsx
@@ -119,7 +119,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
     <fill>
@@ -129,12 +134,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFD966"/>
+        <fgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
     <fill>
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -221,22 +221,22 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -602,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T109"/>
+  <dimension ref="A1:T110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>28</v>
+        <v>41.3</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -836,9 +836,9 @@
           <t>77</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t>77</t>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -881,33 +881,33 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T4" s="9" t="inlineStr">
-        <is>
-          <t>7/7</t>
+      <c r="T4" s="10" t="inlineStr">
+        <is>
+          <t>6/7</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>01_01_2</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="E5" s="10" t="n">
-        <v>27.4</v>
+      <c r="E5" s="11" t="n">
+        <v>40.6</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T5" s="9" t="inlineStr">
+      <c r="T5" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>19.6</v>
+        <v>22.4</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -1077,33 +1077,33 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T6" s="9" t="inlineStr">
+      <c r="T6" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>01_02_2</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="E7" s="10" t="n">
-        <v>17.8</v>
+      <c r="E7" s="11" t="n">
+        <v>21.9</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T7" s="9" t="inlineStr">
+      <c r="T7" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>45.9</v>
+        <v>56.8</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
@@ -1268,34 +1268,34 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="S8" s="11" t="inlineStr"/>
-      <c r="T8" s="12" t="inlineStr">
+      <c r="S8" s="9" t="inlineStr"/>
+      <c r="T8" s="10" t="inlineStr">
         <is>
           <t>6/7</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>01_03_2</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>37.4</v>
+      <c r="E9" s="11" t="n">
+        <v>50.1</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
@@ -1362,8 +1362,8 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="S9" s="11" t="inlineStr"/>
-      <c r="T9" s="12" t="inlineStr">
+      <c r="S9" s="9" t="inlineStr"/>
+      <c r="T9" s="10" t="inlineStr">
         <is>
           <t>6/7</t>
         </is>
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>29.1</v>
+        <v>40.4</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
           <t>14</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="K10" s="9" t="inlineStr">
         <is>
           <t>73</t>
         </is>
@@ -1426,7 +1426,7 @@
           <t>73</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="M10" s="9" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1461,33 +1461,33 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T10" s="12" t="inlineStr">
+      <c r="T10" s="10" t="inlineStr">
         <is>
           <t>5/7</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>01_04_2</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="E11" s="10" t="n">
-        <v>38</v>
+      <c r="E11" s="11" t="n">
+        <v>49.6</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
           <t>14</t>
         </is>
       </c>
-      <c r="M11" s="11" t="inlineStr">
+      <c r="M11" s="9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -1554,8 +1554,8 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="S11" s="11" t="inlineStr"/>
-      <c r="T11" s="12" t="inlineStr">
+      <c r="S11" s="9" t="inlineStr"/>
+      <c r="T11" s="10" t="inlineStr">
         <is>
           <t>5/7</t>
         </is>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>28.9</v>
+        <v>40.6</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -1653,33 +1653,33 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T12" s="9" t="inlineStr">
+      <c r="T12" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="n">
+      <c r="A13" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>01_05_2</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="E13" s="10" t="n">
-        <v>28.5</v>
+      <c r="E13" s="11" t="n">
+        <v>40.5</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T13" s="9" t="inlineStr">
+      <c r="T13" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>28.8</v>
+        <v>42.9</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
           <t>76</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>80</t>
         </is>
@@ -1849,33 +1849,33 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T14" s="12" t="inlineStr">
+      <c r="T14" s="10" t="inlineStr">
         <is>
           <t>6/7</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n">
+      <c r="A15" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>01_06_2</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="E15" s="10" t="n">
-        <v>28.8</v>
+      <c r="E15" s="11" t="n">
+        <v>41.1</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T15" s="9" t="inlineStr">
+      <c r="T15" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>20</v>
+        <v>26.2</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -2045,33 +2045,33 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T16" s="9" t="inlineStr">
+      <c r="T16" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n">
+      <c r="A17" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>01_07_2</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="E17" s="10" t="n">
-        <v>21.4</v>
+      <c r="E17" s="11" t="n">
+        <v>28</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T17" s="9" t="inlineStr">
+      <c r="T17" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>19</v>
+        <v>25.4</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -2241,33 +2241,33 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T18" s="9" t="inlineStr">
+      <c r="T18" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n">
+      <c r="A19" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>01_08_2</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="E19" s="10" t="n">
-        <v>28.6</v>
+      <c r="E19" s="11" t="n">
+        <v>40.6</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T19" s="9" t="inlineStr">
+      <c r="T19" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>29.3</v>
+        <v>41.8</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
@@ -2437,33 +2437,33 @@
           <t>23.1</t>
         </is>
       </c>
-      <c r="T20" s="9" t="inlineStr">
+      <c r="T20" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="n">
+      <c r="A21" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>01_09_2</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
-      <c r="E21" s="10" t="n">
-        <v>18.1</v>
+      <c r="E21" s="11" t="n">
+        <v>23.3</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
           <t>23.1</t>
         </is>
       </c>
-      <c r="T21" s="9" t="inlineStr">
+      <c r="T21" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>30</v>
+        <v>41.8</v>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
@@ -2578,9 +2578,9 @@
           <t>98</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>100</t>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
@@ -2588,9 +2588,9 @@
           <t>74</t>
         </is>
       </c>
-      <c r="K22" s="11" t="inlineStr">
-        <is>
-          <t>98</t>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>74</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
@@ -2635,31 +2635,31 @@
       </c>
       <c r="T22" s="12" t="inlineStr">
         <is>
-          <t>5/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>01_10_2</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
-      <c r="E23" s="10" t="n">
-        <v>29</v>
+      <c r="E23" s="11" t="n">
+        <v>41.6</v>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
@@ -2676,9 +2676,9 @@
           <t>98</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
-        <is>
-          <t>100</t>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
@@ -2686,9 +2686,9 @@
           <t>74</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr">
-        <is>
-          <t>98</t>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>74</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="T23" s="12" t="inlineStr">
         <is>
-          <t>5/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>18.3</v>
+        <v>23.1</v>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
@@ -2829,33 +2829,33 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T24" s="9" t="inlineStr">
+      <c r="T24" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n">
+      <c r="A25" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>02_01_2</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="E25" s="10" t="n">
-        <v>29.1</v>
+      <c r="E25" s="11" t="n">
+        <v>41.5</v>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T25" s="9" t="inlineStr">
+      <c r="T25" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>33.3</v>
+        <v>40.8</v>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
@@ -3025,33 +3025,33 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T26" s="9" t="inlineStr">
+      <c r="T26" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n">
+      <c r="A27" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>02_02_2</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="E27" s="10" t="n">
-        <v>36.1</v>
+      <c r="E27" s="11" t="n">
+        <v>25.6</v>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T27" s="9" t="inlineStr">
+      <c r="T27" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>115.4</v>
+        <v>40.6</v>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
@@ -3221,33 +3221,33 @@
           <t>22.9</t>
         </is>
       </c>
-      <c r="T28" s="9" t="inlineStr">
+      <c r="T28" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
+      <c r="A29" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>02_03_2</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="E29" s="10" t="n">
-        <v>114.3</v>
+      <c r="E29" s="11" t="n">
+        <v>37.8</v>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
           <t>22.9</t>
         </is>
       </c>
-      <c r="T29" s="9" t="inlineStr">
+      <c r="T29" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>92.3</v>
+        <v>40</v>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
@@ -3362,9 +3362,9 @@
           <t>97</t>
         </is>
       </c>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>100</t>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>97</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
@@ -3372,9 +3372,9 @@
           <t>98</t>
         </is>
       </c>
-      <c r="K30" s="11" t="inlineStr">
-        <is>
-          <t>90</t>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
@@ -3402,9 +3402,9 @@
           <t>142</t>
         </is>
       </c>
-      <c r="Q30" s="11" t="inlineStr">
-        <is>
-          <t>82</t>
+      <c r="Q30" s="9" t="inlineStr">
+        <is>
+          <t>86</t>
         </is>
       </c>
       <c r="R30" s="7" t="inlineStr">
@@ -3417,33 +3417,33 @@
           <t>22.9</t>
         </is>
       </c>
-      <c r="T30" s="12" t="inlineStr">
-        <is>
-          <t>4/7</t>
+      <c r="T30" s="10" t="inlineStr">
+        <is>
+          <t>6/7</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n">
+      <c r="A31" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>02_04_2</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="E31" s="10" t="n">
-        <v>98.5</v>
+      <c r="E31" s="11" t="n">
+        <v>39.8</v>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="N31" s="7" t="inlineStr">
@@ -3500,9 +3500,9 @@
           <t>148</t>
         </is>
       </c>
-      <c r="Q31" s="11" t="inlineStr">
-        <is>
-          <t>82</t>
+      <c r="Q31" s="9" t="inlineStr">
+        <is>
+          <t>86</t>
         </is>
       </c>
       <c r="R31" s="7" t="inlineStr">
@@ -3515,7 +3515,7 @@
           <t>22.9</t>
         </is>
       </c>
-      <c r="T31" s="12" t="inlineStr">
+      <c r="T31" s="10" t="inlineStr">
         <is>
           <t>6/7</t>
         </is>
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>57.3</v>
+        <v>53.1</v>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
@@ -3578,9 +3578,9 @@
           <t>17</t>
         </is>
       </c>
-      <c r="M32" s="11" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr">
@@ -3615,31 +3615,31 @@
       </c>
       <c r="T32" s="12" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="n">
+      <c r="A33" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>02_05_2</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="E33" s="10" t="n">
-        <v>58.5</v>
+      <c r="E33" s="11" t="n">
+        <v>55</v>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
@@ -3676,9 +3676,9 @@
           <t>17</t>
         </is>
       </c>
-      <c r="M33" s="11" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="N33" s="7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="T33" s="12" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>72.5</v>
+        <v>45.3</v>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
@@ -3809,33 +3809,33 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T34" s="9" t="inlineStr">
+      <c r="T34" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="n">
+      <c r="A35" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>02_06_2</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="E35" s="10" t="n">
-        <v>58.9</v>
+      <c r="E35" s="11" t="n">
+        <v>52.4</v>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
@@ -3872,9 +3872,9 @@
           <t>17</t>
         </is>
       </c>
-      <c r="M35" s="11" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="M35" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="N35" s="7" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="T35" s="12" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
@@ -3933,14 +3933,14 @@
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>57</v>
+        <v>41.5</v>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr">
         <is>
           <t>193</t>
         </is>
@@ -4005,33 +4005,33 @@
           <t>22.9</t>
         </is>
       </c>
-      <c r="T36" s="12" t="inlineStr">
+      <c r="T36" s="10" t="inlineStr">
         <is>
           <t>6/7</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="n">
+      <c r="A37" s="11" t="n">
         <v>34</v>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>02_07_2</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="E37" s="10" t="n">
-        <v>73.2</v>
+      <c r="E37" s="11" t="n">
+        <v>58.6</v>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
           <t>22.9</t>
         </is>
       </c>
-      <c r="T37" s="9" t="inlineStr">
+      <c r="T37" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>65</v>
+        <v>50.1</v>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
@@ -4201,40 +4201,40 @@
           <t>22.9</t>
         </is>
       </c>
-      <c r="T38" s="9" t="inlineStr">
+      <c r="T38" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="n">
+      <c r="A39" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>02_08_2</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="E39" s="10" t="n">
-        <v>65.3</v>
+      <c r="E39" s="11" t="n">
+        <v>50.9</v>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="G39" s="11" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr">
         <is>
           <t>92</t>
         </is>
@@ -4264,7 +4264,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="M39" s="11" t="inlineStr">
+      <c r="M39" s="9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -4299,7 +4299,7 @@
           <t>22.9</t>
         </is>
       </c>
-      <c r="T39" s="12" t="inlineStr">
+      <c r="T39" s="10" t="inlineStr">
         <is>
           <t>5/7</t>
         </is>
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>91.90000000000001</v>
+        <v>52.3</v>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
@@ -4342,21 +4342,21 @@
           <t>98</t>
         </is>
       </c>
-      <c r="I40" s="11" t="inlineStr">
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="J40" s="7" t="inlineStr">
+      <c r="K40" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="K40" s="11" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
           <t>17</t>
@@ -4399,31 +4399,31 @@
       </c>
       <c r="T40" s="12" t="inlineStr">
         <is>
-          <t>5/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="n">
+      <c r="A41" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>02_09_2</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
-      <c r="E41" s="10" t="n">
-        <v>94.09999999999999</v>
+      <c r="E41" s="11" t="n">
+        <v>72.5</v>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
@@ -4440,9 +4440,9 @@
           <t>98</t>
         </is>
       </c>
-      <c r="I41" s="11" t="inlineStr">
-        <is>
-          <t>100</t>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
         </is>
       </c>
       <c r="J41" s="7" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>97</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="T41" s="12" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>99</v>
+        <v>110.7</v>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
@@ -4538,9 +4538,9 @@
           <t>98</t>
         </is>
       </c>
-      <c r="I42" s="11" t="inlineStr">
-        <is>
-          <t>100</t>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>97</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
@@ -4595,31 +4595,31 @@
       </c>
       <c r="T42" s="12" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="n">
+      <c r="A43" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>02_10_2</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="D43" s="11" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
-      <c r="E43" s="10" t="n">
-        <v>101.6</v>
+      <c r="E43" s="11" t="n">
+        <v>109.9</v>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
@@ -4636,9 +4636,9 @@
           <t>98</t>
         </is>
       </c>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>100</t>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr">
@@ -4646,9 +4646,9 @@
           <t>97</t>
         </is>
       </c>
-      <c r="K43" s="11" t="inlineStr">
-        <is>
-          <t>90</t>
+      <c r="K43" s="8" t="inlineStr">
+        <is>
+          <t>97</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="T43" s="12" t="inlineStr">
         <is>
-          <t>5/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>80.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
@@ -4734,9 +4734,9 @@
           <t>98</t>
         </is>
       </c>
-      <c r="I44" s="11" t="inlineStr">
-        <is>
-          <t>100</t>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
         </is>
       </c>
       <c r="J44" s="7" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
@@ -4791,31 +4791,31 @@
       </c>
       <c r="T44" s="12" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="n">
+      <c r="A45" s="11" t="n">
         <v>42</v>
       </c>
-      <c r="B45" s="10" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>03_01_2</t>
         </is>
       </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D45" s="10" t="inlineStr">
+      <c r="D45" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="E45" s="10" t="n">
-        <v>50.2</v>
+      <c r="E45" s="11" t="n">
+        <v>64.2</v>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T45" s="9" t="inlineStr">
+      <c r="T45" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -4913,7 +4913,7 @@
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>58.3</v>
+        <v>107</v>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
@@ -4930,9 +4930,9 @@
           <t>98</t>
         </is>
       </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>100</t>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr">
@@ -4940,9 +4940,9 @@
           <t>98</t>
         </is>
       </c>
-      <c r="K46" s="11" t="inlineStr">
-        <is>
-          <t>90</t>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
@@ -4987,31 +4987,31 @@
       </c>
       <c r="T46" s="12" t="inlineStr">
         <is>
-          <t>5/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="n">
+      <c r="A47" s="11" t="n">
         <v>44</v>
       </c>
-      <c r="B47" s="10" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>03_02_2</t>
         </is>
       </c>
-      <c r="C47" s="10" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D47" s="10" t="inlineStr">
+      <c r="D47" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="E47" s="10" t="n">
-        <v>56.2</v>
+      <c r="E47" s="11" t="n">
+        <v>108.7</v>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
@@ -5028,9 +5028,9 @@
           <t>98</t>
         </is>
       </c>
-      <c r="I47" s="11" t="inlineStr">
-        <is>
-          <t>100</t>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="T47" s="12" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="E48" s="6" t="n">
-        <v>33.4</v>
+        <v>102</v>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
@@ -5181,33 +5181,33 @@
           <t>22.8</t>
         </is>
       </c>
-      <c r="T48" s="9" t="inlineStr">
+      <c r="T48" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="n">
+      <c r="A49" s="11" t="n">
         <v>46</v>
       </c>
-      <c r="B49" s="10" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>03_03_2</t>
         </is>
       </c>
-      <c r="C49" s="10" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D49" s="10" t="inlineStr">
+      <c r="D49" s="11" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="E49" s="10" t="n">
-        <v>37.2</v>
+      <c r="E49" s="11" t="n">
+        <v>103.7</v>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
@@ -5279,7 +5279,7 @@
           <t>22.8</t>
         </is>
       </c>
-      <c r="T49" s="9" t="inlineStr">
+      <c r="T49" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="E50" s="6" t="n">
-        <v>40.1</v>
+        <v>100.9</v>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
@@ -5377,33 +5377,33 @@
           <t>22.8</t>
         </is>
       </c>
-      <c r="T50" s="9" t="inlineStr">
+      <c r="T50" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="n">
+      <c r="A51" s="11" t="n">
         <v>48</v>
       </c>
-      <c r="B51" s="10" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>03_04_2</t>
         </is>
       </c>
-      <c r="C51" s="10" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D51" s="10" t="inlineStr">
+      <c r="D51" s="11" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="E51" s="10" t="n">
-        <v>33.7</v>
+      <c r="E51" s="11" t="n">
+        <v>108.5</v>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
           <t>22.8</t>
         </is>
       </c>
-      <c r="T51" s="9" t="inlineStr">
+      <c r="T51" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>39.9</v>
+        <v>149.6</v>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
@@ -5538,7 +5538,11 @@
           <t>16</t>
         </is>
       </c>
-      <c r="M52" s="11" t="inlineStr"/>
+      <c r="M52" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
           <t>118/67</t>
@@ -5571,31 +5575,31 @@
       </c>
       <c r="T52" s="12" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="n">
+      <c r="A53" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="B53" s="10" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>03_05_2</t>
         </is>
       </c>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="C53" s="11" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D53" s="10" t="inlineStr">
+      <c r="D53" s="11" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="E53" s="10" t="n">
-        <v>33.5</v>
+      <c r="E53" s="11" t="n">
+        <v>152.5</v>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
@@ -5632,9 +5636,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="M53" s="11" t="inlineStr">
-        <is>
-          <t>6</t>
+      <c r="M53" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
@@ -5669,7 +5673,7 @@
       </c>
       <c r="T53" s="12" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5697,7 @@
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>40.9</v>
+        <v>148.5</v>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
@@ -5730,7 +5734,11 @@
           <t>14</t>
         </is>
       </c>
-      <c r="M54" s="11" t="inlineStr"/>
+      <c r="M54" s="8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
           <t>118/67</t>
@@ -5763,31 +5771,31 @@
       </c>
       <c r="T54" s="12" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="n">
+      <c r="A55" s="11" t="n">
         <v>52</v>
       </c>
-      <c r="B55" s="10" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>03_06_2</t>
         </is>
       </c>
-      <c r="C55" s="10" t="inlineStr">
+      <c r="C55" s="11" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D55" s="10" t="inlineStr">
+      <c r="D55" s="11" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="E55" s="10" t="n">
-        <v>41.1</v>
+      <c r="E55" s="11" t="n">
+        <v>148.2</v>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
@@ -5824,7 +5832,11 @@
           <t>14</t>
         </is>
       </c>
-      <c r="M55" s="11" t="inlineStr"/>
+      <c r="M55" s="8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
           <t>118/67</t>
@@ -5857,7 +5869,7 @@
       </c>
       <c r="T55" s="12" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5893,7 @@
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>40</v>
+        <v>101.3</v>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
@@ -5908,7 +5920,7 @@
           <t>91</t>
         </is>
       </c>
-      <c r="K56" s="11" t="inlineStr">
+      <c r="K56" s="9" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -5953,33 +5965,33 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="T56" s="12" t="inlineStr">
+      <c r="T56" s="10" t="inlineStr">
         <is>
           <t>6/7</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="n">
+      <c r="A57" s="11" t="n">
         <v>54</v>
       </c>
-      <c r="B57" s="10" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>03_07_2</t>
         </is>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C57" s="11" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D57" s="10" t="inlineStr">
+      <c r="D57" s="11" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="E57" s="10" t="n">
-        <v>44</v>
+      <c r="E57" s="11" t="n">
+        <v>106.1</v>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
@@ -6051,7 +6063,7 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="T57" s="9" t="inlineStr">
+      <c r="T57" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -6077,7 +6089,7 @@
         </is>
       </c>
       <c r="E58" s="6" t="n">
-        <v>40.3</v>
+        <v>98.8</v>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
@@ -6149,33 +6161,33 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="T58" s="9" t="inlineStr">
+      <c r="T58" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="n">
+      <c r="A59" s="11" t="n">
         <v>56</v>
       </c>
-      <c r="B59" s="10" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>03_08_2</t>
         </is>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C59" s="11" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D59" s="10" t="inlineStr">
+      <c r="D59" s="11" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="E59" s="10" t="n">
-        <v>39.9</v>
+      <c r="E59" s="11" t="n">
+        <v>100.3</v>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
@@ -6247,7 +6259,7 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="T59" s="9" t="inlineStr">
+      <c r="T59" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -6273,7 +6285,7 @@
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>29.8</v>
+        <v>102.3</v>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
@@ -6345,76 +6357,76 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="T60" s="9" t="inlineStr">
+      <c r="T60" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="n">
+      <c r="A61" s="11" t="n">
         <v>58</v>
       </c>
-      <c r="B61" s="10" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t>03_09_2</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C61" s="11" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D61" s="10" t="inlineStr">
+      <c r="D61" s="11" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
-      <c r="E61" s="10" t="n">
-        <v>45</v>
+      <c r="E61" s="11" t="n">
+        <v>172.3</v>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="G61" s="11" t="inlineStr"/>
+      <c r="G61" s="9" t="inlineStr"/>
       <c r="H61" s="7" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="I61" s="11" t="inlineStr"/>
+      <c r="I61" s="9" t="inlineStr"/>
       <c r="J61" s="7" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="K61" s="11" t="inlineStr"/>
+      <c r="K61" s="9" t="inlineStr"/>
       <c r="L61" s="7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M61" s="11" t="inlineStr"/>
+      <c r="M61" s="9" t="inlineStr"/>
       <c r="N61" s="7" t="inlineStr">
         <is>
           <t>117/81</t>
         </is>
       </c>
-      <c r="O61" s="11" t="inlineStr"/>
+      <c r="O61" s="9" t="inlineStr"/>
       <c r="P61" s="7" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="Q61" s="11" t="inlineStr"/>
+      <c r="Q61" s="9" t="inlineStr"/>
       <c r="R61" s="7" t="inlineStr">
         <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="S61" s="11" t="inlineStr"/>
+      <c r="S61" s="9" t="inlineStr"/>
       <c r="T61" s="13" t="inlineStr">
         <is>
           <t>0/7</t>
@@ -6441,7 +6453,7 @@
         </is>
       </c>
       <c r="E62" s="6" t="n">
-        <v>31.3</v>
+        <v>111.1</v>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
@@ -6513,33 +6525,33 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="T62" s="9" t="inlineStr">
+      <c r="T62" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="n">
+      <c r="A63" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="B63" s="10" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
         <is>
           <t>03_10_2</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C63" s="11" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="D63" s="10" t="inlineStr">
+      <c r="D63" s="11" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
-      <c r="E63" s="10" t="n">
-        <v>28.7</v>
+      <c r="E63" s="11" t="n">
+        <v>84.40000000000001</v>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
@@ -6566,7 +6578,7 @@
           <t>75</t>
         </is>
       </c>
-      <c r="K63" s="11" t="inlineStr"/>
+      <c r="K63" s="9" t="inlineStr"/>
       <c r="L63" s="7" t="inlineStr">
         <is>
           <t>21</t>
@@ -6607,7 +6619,7 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="T63" s="12" t="inlineStr">
+      <c r="T63" s="10" t="inlineStr">
         <is>
           <t>6/7</t>
         </is>
@@ -6633,7 +6645,7 @@
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>38.8</v>
+        <v>10780.9</v>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
@@ -6705,33 +6717,33 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="T64" s="9" t="inlineStr">
+      <c r="T64" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="10" t="n">
+      <c r="A65" s="11" t="n">
         <v>62</v>
       </c>
-      <c r="B65" s="10" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>04_01_2</t>
         </is>
       </c>
-      <c r="C65" s="10" t="inlineStr">
+      <c r="C65" s="11" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="D65" s="10" t="inlineStr">
+      <c r="D65" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="E65" s="10" t="n">
-        <v>33.2</v>
+      <c r="E65" s="11" t="n">
+        <v>45.7</v>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
@@ -6803,7 +6815,7 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="T65" s="9" t="inlineStr">
+      <c r="T65" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -6829,7 +6841,7 @@
         </is>
       </c>
       <c r="E66" s="6" t="n">
-        <v>36.3</v>
+        <v>52.3</v>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
@@ -6901,33 +6913,33 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="T66" s="9" t="inlineStr">
+      <c r="T66" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="10" t="n">
+      <c r="A67" s="11" t="n">
         <v>64</v>
       </c>
-      <c r="B67" s="10" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>04_02_2</t>
         </is>
       </c>
-      <c r="C67" s="10" t="inlineStr">
+      <c r="C67" s="11" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="D67" s="10" t="inlineStr">
+      <c r="D67" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="E67" s="10" t="n">
-        <v>28.1</v>
+      <c r="E67" s="11" t="n">
+        <v>106.8</v>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
@@ -6999,7 +7011,7 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="T67" s="9" t="inlineStr">
+      <c r="T67" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -7025,7 +7037,7 @@
         </is>
       </c>
       <c r="E68" s="6" t="n">
-        <v>28</v>
+        <v>99.8</v>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
@@ -7062,7 +7074,11 @@
           <t>17</t>
         </is>
       </c>
-      <c r="M68" s="11" t="inlineStr"/>
+      <c r="M68" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
           <t>123/80</t>
@@ -7095,31 +7111,31 @@
       </c>
       <c r="T68" s="12" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="10" t="n">
+      <c r="A69" s="11" t="n">
         <v>66</v>
       </c>
-      <c r="B69" s="10" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>04_03_2</t>
         </is>
       </c>
-      <c r="C69" s="10" t="inlineStr">
+      <c r="C69" s="11" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="D69" s="10" t="inlineStr">
+      <c r="D69" s="11" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="E69" s="10" t="n">
-        <v>32.3</v>
+      <c r="E69" s="11" t="n">
+        <v>55.8</v>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
@@ -7136,17 +7152,21 @@
           <t>99</t>
         </is>
       </c>
-      <c r="I69" s="11" t="inlineStr">
+      <c r="I69" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J69" s="7" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="J69" s="7" t="inlineStr">
+      <c r="K69" s="8" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="K69" s="11" t="inlineStr"/>
       <c r="L69" s="7" t="inlineStr">
         <is>
           <t>16</t>
@@ -7189,7 +7209,7 @@
       </c>
       <c r="T69" s="12" t="inlineStr">
         <is>
-          <t>5/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
@@ -7213,14 +7233,14 @@
         </is>
       </c>
       <c r="E70" s="6" t="n">
-        <v>33.7</v>
+        <v>52</v>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="G70" s="11" t="inlineStr">
+      <c r="G70" s="9" t="inlineStr">
         <is>
           <t>57</t>
         </is>
@@ -7285,33 +7305,33 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="T70" s="12" t="inlineStr">
+      <c r="T70" s="10" t="inlineStr">
         <is>
           <t>6/7</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="10" t="n">
+      <c r="A71" s="11" t="n">
         <v>68</v>
       </c>
-      <c r="B71" s="10" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>04_04_2</t>
         </is>
       </c>
-      <c r="C71" s="10" t="inlineStr">
+      <c r="C71" s="11" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="D71" s="10" t="inlineStr">
+      <c r="D71" s="11" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="E71" s="10" t="n">
-        <v>40.9</v>
+      <c r="E71" s="11" t="n">
+        <v>54.7</v>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
@@ -7348,7 +7368,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="M71" s="11" t="inlineStr">
+      <c r="M71" s="9" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -7383,7 +7403,7 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="T71" s="12" t="inlineStr">
+      <c r="T71" s="10" t="inlineStr">
         <is>
           <t>6/7</t>
         </is>
@@ -7409,7 +7429,7 @@
         </is>
       </c>
       <c r="E72" s="6" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
@@ -7466,7 +7486,7 @@
           <t>126</t>
         </is>
       </c>
-      <c r="Q72" s="11" t="inlineStr">
+      <c r="Q72" s="9" t="inlineStr">
         <is>
           <t>79</t>
         </is>
@@ -7481,33 +7501,33 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="T72" s="12" t="inlineStr">
+      <c r="T72" s="10" t="inlineStr">
         <is>
           <t>6/7</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="10" t="n">
+      <c r="A73" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="B73" s="10" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>04_05_2</t>
         </is>
       </c>
-      <c r="C73" s="10" t="inlineStr">
+      <c r="C73" s="11" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="D73" s="10" t="inlineStr">
+      <c r="D73" s="11" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="E73" s="10" t="n">
-        <v>40.9</v>
+      <c r="E73" s="11" t="n">
+        <v>47.2</v>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
@@ -7579,7 +7599,7 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="T73" s="9" t="inlineStr">
+      <c r="T73" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -7605,7 +7625,7 @@
         </is>
       </c>
       <c r="E74" s="6" t="n">
-        <v>39.2</v>
+        <v>46.4</v>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
@@ -7662,7 +7682,7 @@
           <t>126</t>
         </is>
       </c>
-      <c r="Q74" s="11" t="inlineStr">
+      <c r="Q74" s="9" t="inlineStr">
         <is>
           <t>79</t>
         </is>
@@ -7677,33 +7697,33 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="T74" s="12" t="inlineStr">
+      <c r="T74" s="10" t="inlineStr">
         <is>
           <t>6/7</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="10" t="n">
+      <c r="A75" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="B75" s="10" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>04_06_2</t>
         </is>
       </c>
-      <c r="C75" s="10" t="inlineStr">
+      <c r="C75" s="11" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="D75" s="10" t="inlineStr">
+      <c r="D75" s="11" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="E75" s="10" t="n">
-        <v>35.4</v>
+      <c r="E75" s="11" t="n">
+        <v>50</v>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
@@ -7775,7 +7795,7 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="T75" s="9" t="inlineStr">
+      <c r="T75" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -7801,7 +7821,7 @@
         </is>
       </c>
       <c r="E76" s="6" t="n">
-        <v>41.9</v>
+        <v>49.4</v>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
@@ -7873,33 +7893,33 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="T76" s="9" t="inlineStr">
+      <c r="T76" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="n">
+      <c r="A77" s="11" t="n">
         <v>74</v>
       </c>
-      <c r="B77" s="10" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>04_07_2</t>
         </is>
       </c>
-      <c r="C77" s="10" t="inlineStr">
+      <c r="C77" s="11" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="D77" s="10" t="inlineStr">
+      <c r="D77" s="11" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="E77" s="10" t="n">
-        <v>38.2</v>
+      <c r="E77" s="11" t="n">
+        <v>49.9</v>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
@@ -7971,7 +7991,7 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="T77" s="9" t="inlineStr">
+      <c r="T77" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -7997,7 +8017,7 @@
         </is>
       </c>
       <c r="E78" s="6" t="n">
-        <v>70.8</v>
+        <v>56.8</v>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
@@ -8024,7 +8044,7 @@
           <t>81</t>
         </is>
       </c>
-      <c r="K78" s="11" t="inlineStr">
+      <c r="K78" s="9" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -8069,33 +8089,33 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="T78" s="12" t="inlineStr">
+      <c r="T78" s="10" t="inlineStr">
         <is>
           <t>6/7</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="n">
+      <c r="A79" s="11" t="n">
         <v>76</v>
       </c>
-      <c r="B79" s="10" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>04_08_2</t>
         </is>
       </c>
-      <c r="C79" s="10" t="inlineStr">
+      <c r="C79" s="11" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="D79" s="10" t="inlineStr">
+      <c r="D79" s="11" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="E79" s="10" t="n">
-        <v>63.5</v>
+      <c r="E79" s="11" t="n">
+        <v>58.2</v>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
@@ -8167,7 +8187,7 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="T79" s="9" t="inlineStr">
+      <c r="T79" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -8193,7 +8213,7 @@
         </is>
       </c>
       <c r="E80" s="6" t="n">
-        <v>92.5</v>
+        <v>70.5</v>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
@@ -8210,25 +8230,29 @@
           <t>99</t>
         </is>
       </c>
-      <c r="I80" s="11" t="inlineStr">
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J80" s="7" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="J80" s="7" t="inlineStr">
+      <c r="K80" s="8" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="K80" s="11" t="inlineStr"/>
       <c r="L80" s="7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M80" s="11" t="inlineStr">
-        <is>
-          <t>6</t>
+      <c r="M80" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="N80" s="7" t="inlineStr">
@@ -8263,31 +8287,31 @@
       </c>
       <c r="T80" s="12" t="inlineStr">
         <is>
-          <t>4/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="10" t="n">
+      <c r="A81" s="11" t="n">
         <v>78</v>
       </c>
-      <c r="B81" s="10" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
         <is>
           <t>04_09_2</t>
         </is>
       </c>
-      <c r="C81" s="10" t="inlineStr">
+      <c r="C81" s="11" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="D81" s="10" t="inlineStr">
+      <c r="D81" s="11" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
-      <c r="E81" s="10" t="n">
-        <v>113.6</v>
+      <c r="E81" s="11" t="n">
+        <v>69.2</v>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
@@ -8314,9 +8338,9 @@
           <t>84</t>
         </is>
       </c>
-      <c r="K81" s="11" t="inlineStr">
-        <is>
-          <t>80</t>
+      <c r="K81" s="8" t="inlineStr">
+        <is>
+          <t>84</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
@@ -8324,9 +8348,9 @@
           <t>15</t>
         </is>
       </c>
-      <c r="M81" s="11" t="inlineStr">
-        <is>
-          <t>6</t>
+      <c r="M81" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="N81" s="7" t="inlineStr">
@@ -8334,9 +8358,9 @@
           <t>119/56</t>
         </is>
       </c>
-      <c r="O81" s="11" t="inlineStr">
-        <is>
-          <t>119/75</t>
+      <c r="O81" s="8" t="inlineStr">
+        <is>
+          <t>119/56</t>
         </is>
       </c>
       <c r="P81" s="7" t="inlineStr">
@@ -8361,7 +8385,7 @@
       </c>
       <c r="T81" s="12" t="inlineStr">
         <is>
-          <t>4/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
@@ -8385,46 +8409,46 @@
         </is>
       </c>
       <c r="E82" s="6" t="n">
-        <v>111.1</v>
+        <v>59</v>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="G82" s="8" t="inlineStr">
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J82" s="7" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="H82" s="7" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="I82" s="11" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J82" s="7" t="inlineStr">
+      <c r="K82" s="8" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="K82" s="11" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M82" s="8" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="M82" s="9" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="N82" s="7" t="inlineStr">
@@ -8432,9 +8456,9 @@
           <t>119/56</t>
         </is>
       </c>
-      <c r="O82" s="8" t="inlineStr">
-        <is>
-          <t>119/56</t>
+      <c r="O82" s="9" t="inlineStr">
+        <is>
+          <t>102/56</t>
         </is>
       </c>
       <c r="P82" s="7" t="inlineStr">
@@ -8452,67 +8476,63 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="S82" s="8" t="inlineStr">
-        <is>
-          <t>22.1</t>
-        </is>
-      </c>
-      <c r="T82" s="12" t="inlineStr">
-        <is>
-          <t>5/7</t>
+      <c r="S82" s="9" t="inlineStr"/>
+      <c r="T82" s="10" t="inlineStr">
+        <is>
+          <t>3/7</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="10" t="n">
+      <c r="A83" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="B83" s="10" t="inlineStr">
-        <is>
-          <t>05_01_1</t>
-        </is>
-      </c>
-      <c r="C83" s="10" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="D83" s="10" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>60.2</v>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>04_10_2</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="n">
+        <v>76.40000000000001</v>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>99</t>
         </is>
       </c>
       <c r="I83" s="8" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K83" s="8" t="inlineStr">
-        <is>
-          <t>91</t>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K83" s="9" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
@@ -8520,29 +8540,25 @@
           <t>15</t>
         </is>
       </c>
-      <c r="M83" s="8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="M83" s="9" t="inlineStr"/>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>123/80</t>
-        </is>
-      </c>
-      <c r="O83" s="8" t="inlineStr">
-        <is>
-          <t>123/80</t>
+          <t>119/56</t>
+        </is>
+      </c>
+      <c r="O83" s="9" t="inlineStr">
+        <is>
+          <t>1/56</t>
         </is>
       </c>
       <c r="P83" s="7" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>61</t>
         </is>
       </c>
       <c r="Q83" s="8" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>61</t>
         </is>
       </c>
       <c r="R83" s="7" t="inlineStr">
@@ -8550,14 +8566,10 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="S83" s="8" t="inlineStr">
-        <is>
-          <t>22.7</t>
-        </is>
-      </c>
-      <c r="T83" s="9" t="inlineStr">
-        <is>
-          <t>7/7</t>
+      <c r="S83" s="9" t="inlineStr"/>
+      <c r="T83" s="10" t="inlineStr">
+        <is>
+          <t>3/7</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8579,7 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>05_01_2</t>
+          <t>05_01_1</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
@@ -8581,7 +8593,7 @@
         </is>
       </c>
       <c r="E84" s="6" t="n">
-        <v>44.8</v>
+        <v>35.4</v>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
@@ -8595,22 +8607,22 @@
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J84" s="7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K84" s="8" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="L84" s="7" t="inlineStr">
@@ -8635,12 +8647,12 @@
       </c>
       <c r="P84" s="7" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>91</t>
         </is>
       </c>
       <c r="Q84" s="8" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>91</t>
         </is>
       </c>
       <c r="R84" s="7" t="inlineStr">
@@ -8653,33 +8665,33 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="T84" s="9" t="inlineStr">
+      <c r="T84" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="10" t="n">
+      <c r="A85" s="11" t="n">
         <v>82</v>
       </c>
-      <c r="B85" s="10" t="inlineStr">
-        <is>
-          <t>05_02_1</t>
-        </is>
-      </c>
-      <c r="C85" s="10" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>05_01_2</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="D85" s="10" t="inlineStr">
+      <c r="D85" s="11" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="E85" s="10" t="n">
-        <v>37.8</v>
+      <c r="E85" s="11" t="n">
+        <v>33.2</v>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
@@ -8693,24 +8705,24 @@
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="I85" s="8" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="J85" s="7" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="I85" s="8" t="inlineStr">
+      <c r="K85" s="8" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="J85" s="7" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K85" s="8" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
           <t>15</t>
@@ -8733,12 +8745,12 @@
       </c>
       <c r="P85" s="7" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>94</t>
         </is>
       </c>
       <c r="Q85" s="8" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>94</t>
         </is>
       </c>
       <c r="R85" s="7" t="inlineStr">
@@ -8751,7 +8763,7 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="T85" s="9" t="inlineStr">
+      <c r="T85" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -8763,7 +8775,7 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>05_02_2</t>
+          <t>05_02_1</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
@@ -8777,7 +8789,7 @@
         </is>
       </c>
       <c r="E86" s="6" t="n">
-        <v>45.6</v>
+        <v>37</v>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
@@ -8791,22 +8803,22 @@
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I86" s="8" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J86" s="7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K86" s="8" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>91</t>
         </is>
       </c>
       <c r="L86" s="7" t="inlineStr">
@@ -8831,12 +8843,12 @@
       </c>
       <c r="P86" s="7" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>91</t>
         </is>
       </c>
       <c r="Q86" s="8" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>91</t>
         </is>
       </c>
       <c r="R86" s="7" t="inlineStr">
@@ -8849,67 +8861,67 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="T86" s="9" t="inlineStr">
+      <c r="T86" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="10" t="n">
+      <c r="A87" s="11" t="n">
         <v>84</v>
       </c>
-      <c r="B87" s="10" t="inlineStr">
-        <is>
-          <t>05_03_1</t>
-        </is>
-      </c>
-      <c r="C87" s="10" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>05_02_2</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="D87" s="10" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>130.8</v>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="n">
+        <v>31.5</v>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="I87" s="8" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="J87" s="7" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="G87" s="8" t="inlineStr">
+      <c r="K87" s="8" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="H87" s="7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="I87" s="8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J87" s="7" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K87" s="8" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M87" s="8" t="inlineStr">
@@ -8919,35 +8931,35 @@
       </c>
       <c r="N87" s="7" t="inlineStr">
         <is>
-          <t>102/84</t>
+          <t>123/80</t>
         </is>
       </c>
       <c r="O87" s="8" t="inlineStr">
         <is>
-          <t>102/84</t>
+          <t>123/80</t>
         </is>
       </c>
       <c r="P87" s="7" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>94</t>
         </is>
       </c>
       <c r="Q87" s="8" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>94</t>
         </is>
       </c>
       <c r="R87" s="7" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="S87" s="8" t="inlineStr">
         <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="T87" s="9" t="inlineStr">
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T87" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -8959,7 +8971,7 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>05_03_2</t>
+          <t>05_03_1</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
@@ -8973,16 +8985,16 @@
         </is>
       </c>
       <c r="E88" s="6" t="n">
-        <v>93.7</v>
+        <v>53</v>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
@@ -8997,12 +9009,12 @@
       </c>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K88" s="8" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>93</t>
         </is>
       </c>
       <c r="L88" s="7" t="inlineStr">
@@ -9010,9 +9022,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="M88" s="11" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="M88" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="N88" s="7" t="inlineStr">
@@ -9047,40 +9059,40 @@
       </c>
       <c r="T88" s="12" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="10" t="n">
+      <c r="A89" s="11" t="n">
         <v>86</v>
       </c>
-      <c r="B89" s="10" t="inlineStr">
-        <is>
-          <t>05_04_1</t>
-        </is>
-      </c>
-      <c r="C89" s="10" t="inlineStr">
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>05_03_2</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="D89" s="10" t="inlineStr">
+      <c r="D89" s="11" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="E89" s="10" t="n">
-        <v>108.5</v>
+      <c r="E89" s="11" t="n">
+        <v>55.7</v>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>92</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
@@ -9088,21 +9100,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="I89" s="8" t="inlineStr">
-        <is>
-          <t>100</t>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>95</t>
         </is>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K89" s="8" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="K89" s="9" t="inlineStr"/>
       <c r="L89" s="7" t="inlineStr">
         <is>
           <t>16</t>
@@ -9143,9 +9151,9 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="T89" s="9" t="inlineStr">
-        <is>
-          <t>7/7</t>
+      <c r="T89" s="10" t="inlineStr">
+        <is>
+          <t>5/7</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9163,7 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>05_04_2</t>
+          <t>05_04_1</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
@@ -9169,16 +9177,16 @@
         </is>
       </c>
       <c r="E90" s="6" t="n">
-        <v>94.09999999999999</v>
+        <v>55.4</v>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
@@ -9193,12 +9201,12 @@
       </c>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K90" s="8" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>93</t>
         </is>
       </c>
       <c r="L90" s="7" t="inlineStr">
@@ -9241,42 +9249,42 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="T90" s="9" t="inlineStr">
+      <c r="T90" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="10" t="n">
+      <c r="A91" s="11" t="n">
         <v>88</v>
       </c>
-      <c r="B91" s="10" t="inlineStr">
-        <is>
-          <t>05_05_1</t>
-        </is>
-      </c>
-      <c r="C91" s="10" t="inlineStr">
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>05_04_2</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="D91" s="10" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>35.5</v>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>Left</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="n">
+        <v>60.1</v>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>92</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
@@ -9291,22 +9299,22 @@
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="K91" s="8" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M91" s="8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N91" s="7" t="inlineStr">
@@ -9339,7 +9347,7 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="T91" s="9" t="inlineStr">
+      <c r="T91" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -9351,7 +9359,7 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>05_05_2</t>
+          <t>05_05_1</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
@@ -9365,16 +9373,16 @@
         </is>
       </c>
       <c r="E92" s="6" t="n">
-        <v>37.9</v>
+        <v>26.4</v>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>98</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
@@ -9389,12 +9397,12 @@
       </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K92" s="8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>96</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
@@ -9437,64 +9445,64 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="T92" s="9" t="inlineStr">
+      <c r="T92" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="10" t="n">
+      <c r="A93" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="B93" s="10" t="inlineStr">
-        <is>
-          <t>05_06_1</t>
-        </is>
-      </c>
-      <c r="C93" s="10" t="inlineStr">
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>05_05_2</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="D93" s="10" t="inlineStr">
+      <c r="D93" s="11" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="E93" s="10" t="n">
-        <v>36.9</v>
+      <c r="E93" s="11" t="n">
+        <v>29.8</v>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I93" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J93" s="7" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="G93" s="8" t="inlineStr">
+      <c r="K93" s="8" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="H93" s="7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="I93" s="8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J93" s="7" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K93" s="8" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
           <t>17</t>
@@ -9535,7 +9543,7 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="T93" s="9" t="inlineStr">
+      <c r="T93" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -9547,7 +9555,7 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>05_06_2</t>
+          <t>05_06_1</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
@@ -9561,16 +9569,16 @@
         </is>
       </c>
       <c r="E94" s="6" t="n">
-        <v>57.7</v>
+        <v>24.8</v>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>98</t>
         </is>
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
@@ -9585,12 +9593,12 @@
       </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K94" s="8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>96</t>
         </is>
       </c>
       <c r="L94" s="7" t="inlineStr">
@@ -9633,107 +9641,103 @@
           <t>22.6</t>
         </is>
       </c>
-      <c r="T94" s="9" t="inlineStr">
+      <c r="T94" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="10" t="n">
+      <c r="A95" s="11" t="n">
         <v>92</v>
       </c>
-      <c r="B95" s="10" t="inlineStr">
-        <is>
-          <t>05_07_1</t>
-        </is>
-      </c>
-      <c r="C95" s="10" t="inlineStr">
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>05_06_2</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="D95" s="10" t="inlineStr">
-        <is>
-          <t>Up</t>
-        </is>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>51.7</v>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="n">
+        <v>52.3</v>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>99</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="I95" s="8" t="inlineStr">
-        <is>
-          <t>93</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>98</t>
         </is>
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K95" s="8" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K95" s="9" t="inlineStr"/>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="M95" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="N95" s="7" t="inlineStr">
         <is>
-          <t>69/57</t>
+          <t>102/84</t>
         </is>
       </c>
       <c r="O95" s="8" t="inlineStr">
         <is>
-          <t>69/57</t>
+          <t>102/84</t>
         </is>
       </c>
       <c r="P95" s="7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>87</t>
         </is>
       </c>
       <c r="Q95" s="8" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>87</t>
         </is>
       </c>
       <c r="R95" s="7" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="S95" s="8" t="inlineStr">
         <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="T95" s="9" t="inlineStr">
-        <is>
-          <t>7/7</t>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="T95" s="10" t="inlineStr">
+        <is>
+          <t>5/7</t>
         </is>
       </c>
     </row>
@@ -9743,7 +9747,7 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>05_07_2</t>
+          <t>05_07_1</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
@@ -9757,34 +9761,38 @@
         </is>
       </c>
       <c r="E96" s="6" t="n">
-        <v>50.7</v>
+        <v>70.7</v>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="G96" s="11" t="inlineStr">
+          <t>86</t>
+        </is>
+      </c>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="H96" s="7" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="H96" s="7" t="inlineStr">
+      <c r="I96" s="8" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="I96" s="11" t="inlineStr">
+      <c r="J96" s="7" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="J96" s="7" t="inlineStr">
+      <c r="K96" s="8" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="K96" s="11" t="inlineStr"/>
       <c r="L96" s="7" t="inlineStr">
         <is>
           <t>11</t>
@@ -9807,12 +9815,12 @@
       </c>
       <c r="P96" s="7" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Q96" s="8" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>65</t>
         </is>
       </c>
       <c r="R96" s="7" t="inlineStr">
@@ -9827,40 +9835,40 @@
       </c>
       <c r="T96" s="12" t="inlineStr">
         <is>
-          <t>4/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="10" t="n">
+      <c r="A97" s="11" t="n">
         <v>94</v>
       </c>
-      <c r="B97" s="10" t="inlineStr">
-        <is>
-          <t>05_08_1</t>
-        </is>
-      </c>
-      <c r="C97" s="10" t="inlineStr">
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>05_07_2</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="D97" s="10" t="inlineStr">
+      <c r="D97" s="11" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="E97" s="10" t="n">
-        <v>53.3</v>
+      <c r="E97" s="11" t="n">
+        <v>54.3</v>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="G97" s="8" t="inlineStr">
-        <is>
-          <t>86</t>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G97" s="9" t="inlineStr">
+        <is>
+          <t>88</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
@@ -9905,12 +9913,12 @@
       </c>
       <c r="P97" s="7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>62</t>
         </is>
       </c>
       <c r="Q97" s="8" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>62</t>
         </is>
       </c>
       <c r="R97" s="7" t="inlineStr">
@@ -9923,9 +9931,9 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="T97" s="9" t="inlineStr">
-        <is>
-          <t>7/7</t>
+      <c r="T97" s="10" t="inlineStr">
+        <is>
+          <t>6/7</t>
         </is>
       </c>
     </row>
@@ -9935,7 +9943,7 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>05_08_2</t>
+          <t>05_08_1</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
@@ -9949,34 +9957,38 @@
         </is>
       </c>
       <c r="E98" s="6" t="n">
-        <v>48.1</v>
+        <v>65.5</v>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="G98" s="11" t="inlineStr">
+          <t>86</t>
+        </is>
+      </c>
+      <c r="G98" s="8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="H98" s="7" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="H98" s="7" t="inlineStr">
+      <c r="I98" s="8" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="I98" s="11" t="inlineStr">
+      <c r="J98" s="7" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="J98" s="7" t="inlineStr">
+      <c r="K98" s="8" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="K98" s="11" t="inlineStr"/>
       <c r="L98" s="7" t="inlineStr">
         <is>
           <t>11</t>
@@ -9999,12 +10011,12 @@
       </c>
       <c r="P98" s="7" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Q98" s="8" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>65</t>
         </is>
       </c>
       <c r="R98" s="7" t="inlineStr">
@@ -10019,105 +10031,105 @@
       </c>
       <c r="T98" s="12" t="inlineStr">
         <is>
-          <t>4/7</t>
+          <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="10" t="n">
+      <c r="A99" s="11" t="n">
         <v>96</v>
       </c>
-      <c r="B99" s="10" t="inlineStr">
-        <is>
-          <t>05_09_1</t>
-        </is>
-      </c>
-      <c r="C99" s="10" t="inlineStr">
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>05_08_2</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="D99" s="10" t="inlineStr">
-        <is>
-          <t>Down</t>
-        </is>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>45.8</v>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v>53.9</v>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="G99" s="8" t="inlineStr">
-        <is>
-          <t>95</t>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G99" s="9" t="inlineStr">
+        <is>
+          <t>88</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>93</t>
         </is>
       </c>
       <c r="I99" s="8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>93</t>
         </is>
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K99" s="8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>88</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N99" s="7" t="inlineStr">
         <is>
-          <t>102/84</t>
+          <t>69/57</t>
         </is>
       </c>
       <c r="O99" s="8" t="inlineStr">
         <is>
-          <t>102/84</t>
+          <t>69/57</t>
         </is>
       </c>
       <c r="P99" s="7" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>62</t>
         </is>
       </c>
       <c r="Q99" s="8" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>62</t>
         </is>
       </c>
       <c r="R99" s="7" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="S99" s="8" t="inlineStr">
         <is>
-          <t>22.7</t>
-        </is>
-      </c>
-      <c r="T99" s="9" t="inlineStr">
-        <is>
-          <t>7/7</t>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="T99" s="10" t="inlineStr">
+        <is>
+          <t>6/7</t>
         </is>
       </c>
     </row>
@@ -10127,7 +10139,7 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>05_09_2</t>
+          <t>05_09_1</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
@@ -10141,16 +10153,16 @@
         </is>
       </c>
       <c r="E100" s="6" t="n">
-        <v>47.6</v>
+        <v>49.7</v>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>95</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
@@ -10165,12 +10177,12 @@
       </c>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K100" s="8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>98</t>
         </is>
       </c>
       <c r="L100" s="7" t="inlineStr">
@@ -10213,42 +10225,42 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="T100" s="9" t="inlineStr">
+      <c r="T100" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="10" t="n">
+      <c r="A101" s="11" t="n">
         <v>98</v>
       </c>
-      <c r="B101" s="10" t="inlineStr">
-        <is>
-          <t>05_10_1</t>
-        </is>
-      </c>
-      <c r="C101" s="10" t="inlineStr">
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>05_09_2</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="D101" s="10" t="inlineStr">
+      <c r="D101" s="11" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
-      <c r="E101" s="10" t="n">
-        <v>56.3</v>
+      <c r="E101" s="11" t="n">
+        <v>53.3</v>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>99</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H101" s="7" t="inlineStr">
@@ -10263,12 +10275,12 @@
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K101" s="8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>100</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
@@ -10311,7 +10323,7 @@
           <t>22.7</t>
         </is>
       </c>
-      <c r="T101" s="9" t="inlineStr">
+      <c r="T101" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
         </is>
@@ -10323,252 +10335,350 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
+          <t>05_10_1</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H102" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I102" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J102" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K102" s="8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M102" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N102" s="7" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="O102" s="8" t="inlineStr">
+        <is>
+          <t>102/84</t>
+        </is>
+      </c>
+      <c r="P102" s="7" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="Q102" s="8" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="R102" s="7" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="S102" s="8" t="inlineStr">
+        <is>
+          <t>22.7</t>
+        </is>
+      </c>
+      <c r="T102" s="12" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
           <t>05_10_2</t>
         </is>
       </c>
-      <c r="C102" s="6" t="inlineStr">
+      <c r="C103" s="11" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="D102" s="6" t="inlineStr">
+      <c r="D103" s="11" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
       </c>
-      <c r="E102" s="6" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="F102" s="7" t="inlineStr">
+      <c r="E103" s="11" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="G102" s="8" t="inlineStr">
+      <c r="G103" s="8" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="H102" s="7" t="inlineStr">
+      <c r="H103" s="7" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="I102" s="8" t="inlineStr">
+      <c r="I103" s="8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="J102" s="7" t="inlineStr">
+      <c r="J103" s="7" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="K102" s="8" t="inlineStr">
+      <c r="K103" s="8" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="L102" s="7" t="inlineStr">
+      <c r="L103" s="7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="M102" s="8" t="inlineStr">
+      <c r="M103" s="8" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N102" s="7" t="inlineStr">
+      <c r="N103" s="7" t="inlineStr">
         <is>
           <t>102/84</t>
         </is>
       </c>
-      <c r="O102" s="8" t="inlineStr">
+      <c r="O103" s="8" t="inlineStr">
         <is>
           <t>102/84</t>
         </is>
       </c>
-      <c r="P102" s="7" t="inlineStr">
+      <c r="P103" s="7" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="Q102" s="8" t="inlineStr">
+      <c r="Q103" s="8" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="R102" s="7" t="inlineStr">
+      <c r="R103" s="7" t="inlineStr">
         <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="S102" s="8" t="inlineStr">
+      <c r="S103" s="8" t="inlineStr">
         <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="T102" s="9" t="inlineStr">
+      <c r="T103" s="12" t="inlineStr">
         <is>
           <t>7/7</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="14" t="inlineStr">
-        <is>
-          <t>ACCURACY SUMMARY</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="15" t="inlineStr">
-        <is>
-          <t>Accuracy %</t>
-        </is>
-      </c>
-      <c r="B105" s="16" t="n"/>
-      <c r="C105" s="16" t="n"/>
-      <c r="D105" s="16" t="n"/>
-      <c r="E105" s="16" t="n"/>
-      <c r="F105" s="17" t="inlineStr">
-        <is>
-          <t>93/99</t>
-        </is>
-      </c>
-      <c r="G105" s="18" t="inlineStr">
-        <is>
-          <t>93.9%</t>
-        </is>
-      </c>
-      <c r="H105" s="17" t="inlineStr">
-        <is>
-          <t>83/99</t>
-        </is>
-      </c>
-      <c r="I105" s="18" t="inlineStr">
-        <is>
-          <t>83.8%</t>
-        </is>
-      </c>
-      <c r="J105" s="17" t="inlineStr">
-        <is>
-          <t>81/99</t>
-        </is>
-      </c>
-      <c r="K105" s="18" t="inlineStr">
-        <is>
-          <t>81.8%</t>
-        </is>
-      </c>
-      <c r="L105" s="17" t="inlineStr">
-        <is>
-          <t>83/99</t>
-        </is>
-      </c>
-      <c r="M105" s="18" t="inlineStr">
-        <is>
-          <t>83.8%</t>
-        </is>
-      </c>
-      <c r="N105" s="17" t="inlineStr">
-        <is>
-          <t>97/99</t>
-        </is>
-      </c>
-      <c r="O105" s="18" t="inlineStr">
-        <is>
-          <t>98.0%</t>
-        </is>
-      </c>
-      <c r="P105" s="17" t="inlineStr">
-        <is>
-          <t>94/99</t>
-        </is>
-      </c>
-      <c r="Q105" s="18" t="inlineStr">
-        <is>
-          <t>94.9%</t>
-        </is>
-      </c>
-      <c r="R105" s="17" t="inlineStr">
-        <is>
-          <t>95/99</t>
-        </is>
-      </c>
-      <c r="S105" s="18" t="inlineStr">
-        <is>
-          <t>96.0%</t>
+      <c r="A105" s="14" t="inlineStr">
+        <is>
+          <t>ACCURACY SUMMARY</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="19" t="inlineStr">
+      <c r="A106" s="15" t="inlineStr">
+        <is>
+          <t>Accuracy %</t>
+        </is>
+      </c>
+      <c r="B106" s="16" t="n"/>
+      <c r="C106" s="16" t="n"/>
+      <c r="D106" s="16" t="n"/>
+      <c r="E106" s="16" t="n"/>
+      <c r="F106" s="17" t="inlineStr">
+        <is>
+          <t>93/100</t>
+        </is>
+      </c>
+      <c r="G106" s="18" t="inlineStr">
+        <is>
+          <t>93.0%</t>
+        </is>
+      </c>
+      <c r="H106" s="17" t="inlineStr">
+        <is>
+          <t>97/100</t>
+        </is>
+      </c>
+      <c r="I106" s="18" t="inlineStr">
+        <is>
+          <t>97.0%</t>
+        </is>
+      </c>
+      <c r="J106" s="17" t="inlineStr">
+        <is>
+          <t>90/100</t>
+        </is>
+      </c>
+      <c r="K106" s="18" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+      <c r="L106" s="17" t="inlineStr">
+        <is>
+          <t>93/100</t>
+        </is>
+      </c>
+      <c r="M106" s="18" t="inlineStr">
+        <is>
+          <t>93.0%</t>
+        </is>
+      </c>
+      <c r="N106" s="17" t="inlineStr">
+        <is>
+          <t>97/100</t>
+        </is>
+      </c>
+      <c r="O106" s="18" t="inlineStr">
+        <is>
+          <t>97.0%</t>
+        </is>
+      </c>
+      <c r="P106" s="17" t="inlineStr">
+        <is>
+          <t>95/100</t>
+        </is>
+      </c>
+      <c r="Q106" s="18" t="inlineStr">
+        <is>
+          <t>95.0%</t>
+        </is>
+      </c>
+      <c r="R106" s="17" t="inlineStr">
+        <is>
+          <t>94/100</t>
+        </is>
+      </c>
+      <c r="S106" s="18" t="inlineStr">
+        <is>
+          <t>94.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="19" t="inlineStr">
         <is>
           <t>All Correct</t>
         </is>
       </c>
-      <c r="F106" s="20" t="inlineStr">
-        <is>
-          <t>58 / 99  (58.6%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="21" t="inlineStr">
-        <is>
-          <t>Legend:</t>
+      <c r="F107" s="20" t="inlineStr">
+        <is>
+          <t>76 / 100  (76.0%)</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="22" t="inlineStr">
+      <c r="A109" s="21" t="inlineStr">
+        <is>
+          <t>Legend:</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
-      <c r="B109" s="23" t="inlineStr">
+      <c r="B110" s="23" t="inlineStr">
         <is>
           <t>Correct prediction</t>
         </is>
       </c>
-      <c r="C109" s="24" t="inlineStr">
+      <c r="C110" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
-      <c r="D109" s="23" t="inlineStr">
+      <c r="D110" s="23" t="inlineStr">
         <is>
           <t>Wrong prediction</t>
         </is>
       </c>
-      <c r="E109" s="25" t="inlineStr">
+      <c r="E110" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
-      <c r="F109" s="23" t="inlineStr">
+      <c r="F110" s="23" t="inlineStr">
         <is>
           <t>Ground truth value</t>
         </is>
       </c>
-      <c r="G109" s="26" t="inlineStr">
+      <c r="G110" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
-      <c r="H109" s="23" t="inlineStr">
+      <c r="H110" s="23" t="inlineStr">
         <is>
           <t>All vitals correct</t>
         </is>
       </c>
-      <c r="I109" s="27" t="inlineStr">
+      <c r="I110" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
         </is>
       </c>
-      <c r="J109" s="23" t="inlineStr">
+      <c r="J110" s="23" t="inlineStr">
         <is>
           <t>Some vitals wrong</t>
         </is>
@@ -10577,16 +10687,16 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="L2:M2"/>
-    <mergeCell ref="F106:T106"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="F1:S1"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="N2:O2"/>
+    <mergeCell ref="F107:T107"/>
     <mergeCell ref="R2:S2"/>
     <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="A107:E107"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A106:E106"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
